--- a/docs/exports/week-2026-10-18.xlsx
+++ b/docs/exports/week-2026-10-18.xlsx
@@ -538,21 +538,21 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">熊本晶圓計畫核准與台灣設備服務收購授權
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>日本 10/16 核准 JASM 二廠變更計畫，台灣光罩同日改由母公司擬收購熊本 TCK。前者仍在建置，後者尚未確認交割，分別對應製程建置與在地設備服務。</t>
+            <t xml:space="preserve">越南與 EFTA 簽署協定，設備與投資規則待對照生效條件
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>越南與 EFTA 四國 10/18 在河內簽署協定，涵蓋貨品、服務、投資、原產地及政府採購。工業設備與電機是既有貿易項目，生效日期和逐項產品待遇尚不能僅由簽署公告認定。</t>
           </r>
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>46311</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
@@ -570,16 +570,16 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">馬來西亞六項晶片創新涵蓋儲存、工業控制與電源
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>10/16 發表的六項創新包括 AI 處理器、儲存、FPGA、車用與衛星電源控制等。部長估計 3 億令吉合計銷售潛力但未列期間，客戶認證與量產數量仍待公布。</t>
+            <t xml:space="preserve">熊本晶圓計畫核准與在地設備服務收購授權
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>據專業報導，日本 10/16 核准 JASM 二廠首階段 3 奈米計畫，台灣光罩同日改由母公司擬收購 TCK。晶圓產能仍為建置規劃，設備服務收購尚未確認交割，原始核准文件與公告取得範圍有限。</t>
           </r>
         </is>
       </c>
@@ -602,21 +602,21 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">越南軋鋼產線核心設備合約落定
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>VinMetal 與 Danieli 10/15 簽訂核心設備合約，專案位於河靜永安經濟區。逾 70 萬噸為單條產線年設計能力，交付、投產與客戶驗收時程尚未公布。</t>
+            <t xml:space="preserve">鴻海擬取得三菱電機移動半數股權，合作涵蓋電動動力與控制
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>10/16 協議將 50% 股權對價定為 1,150 億日圓，標的全部股權價值為 2,300 億日圓。預定 2027/10/1 交割，仍待核准及契約條件；公告未提供新增出貨或工廠產量。</t>
           </r>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
@@ -634,21 +634,23 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">泰國材料用地與柔佛智慧園區分處規劃階段
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>榮科 10/16 通過泰國子公司購地案，價款與廠址待定；同日報導 Genting 與華為規劃古來 430 英畝智慧園區。兩案均未提供可核實的新增量產、租戶或實付投資數字。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>46311</v>
+            <t xml:space="preserve">台灣儲能合作、燃料調度與風電工程各有不同完成節點
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>鴻海團隊 10/16 公布 306 kWh 表後儲能櫃規劃與 2027 上半年供貨目標，經部 10/18 稱中油已展開次年首季採購。離岸二期累計四部完成安裝為經部轉述，尚未等同併網，聯貸付款爭議也未有最終清償安排。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>10/16、10/18</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
@@ -666,21 +668,21 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">越南提出 2027 成長目標與 2026 全年貿易估計
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>越南政府 10/17 向國會提出次年 GDP 至少成長 10%、CPI 約 4.5% 及生產力成長 8.6% 目標。2026 年商品進出口估計 1.11 兆美元，目標與估計皆須與已完成實績分開閱讀。</t>
+            <t xml:space="preserve">新加坡電子外銷與馬來西亞晶片發表分屬出貨及開發資料
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>新加坡 10/16 公布 9 月 NODX 年增 68.4%、對台年增 96.9%，總體增幅包含船體低基期因素。馬來西亞同日發表六項本土晶片創新，3 億令吉銷售潛力無明確期間，發表場館記載亦有差異。</t>
           </r>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
     </row>
   </sheetData>
@@ -699,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -752,25 +754,25 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">追蹤：日本核准 JASM 熊本二廠變更計畫，首階段規劃 3 奈米月產 6,000 片
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>據 Reuters 與中央社報導，日本經產省 10 月 16 日核准台積電旗下 JASM 熊本第二工廠的變更計畫，首階段規劃每月生產 6,000 片 3 奈米晶圓。新增進展是計畫獲准；3 奈米轉向已於 2 月公布，工廠仍在建設，產能數字屬規劃。JASM 為台積電在日本的製造子公司，二廠設於熊本既有廠區旁。這次核准連結晶圓製程與設備建置，並未包含新的 HBM、封裝測試或伺服器出貨資料。中央社報導新計畫預定 2028 年底投產。先前的月產 4.8 萬片規劃涵蓋不同製程與建置範圍，不能直接與首階段 3 奈米月產 6,000 片計算減產率。未直接取得經產省核准文件，產能與時程依專業報導；設備名單、良率與實際量產能力尚未公布。地點：專案地點：日本熊本縣，JASM 第二工廠，鄰近既有第一工廠。</t>
+            <t xml:space="preserve">越南與 EFTA 四國簽署自由貿易協定，涵蓋工業品、原產地與投資規則
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>越南與瑞士、挪威、冰島、列支敦斯登 10 月 18 日在河內簽署自由貿易協定，涵蓋貨品、服務、原產地、投資及政府採購。電機與機械已是雙方貿易項目，但簽署不代表所有產品當日免稅；生效日與各產品優惠條件仍須以正式文本及附表確認。EFTA 指出，電機與機械均列於既有雙邊貨品貿易中。越南工商部列出的協定範圍包含關稅、技術性貿易障礙、海關程序及投資；公告沒有列出受惠供應商或新建產線名單。雙方 7 月 2 日結束談判，10 月 18 日完成簽署。EFTA 提供的章節說明仍為 7 月版本，列有產品別原產地規則；簽署、完成國內程序與優惠實際適用是不同階段。所閱公告未確立生效日期或逐項產品優惠時程；個別設備稅則、原產地及認證適用仍須依正式協定與附表確認。地點：簽署地點：越南河內；所閱官方公告未列具體會議場館。</t>
           </r>
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>46311</v>
+        <v>46313</v>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>對蝕刻、沉積用精密電源與量測設備業者而言，相關客戶是晶圓廠及其製程設備商。值得追問的是 3 奈米設備認證、進機與驗收時程；計畫月產能尚不足以推定設備採購量或供應商訂單。</t>
+          <t>對精密電源與量測控制設備供應商而言，相關環節是越南工廠設備與測試產品的跨境交易。值得核對的是產品稅則、原產地與認證條件在正式生效文本中的適用；目前沒有客戶採購資料，不能由協定簽署推定新增訂單。</t>
         </is>
       </c>
     </row>
@@ -789,16 +791,16 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">追蹤：台灣光罩改由母公司擬收購熊本 TCK，授權上限 7.5 億日圓
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>台灣光罩 10 月 16 日董事會授權董事長在 7.5 億日圓內取得日本熊本設備服務商 TCK 的全部股權，中央社換算約新台幣 1.6 億元。相較 7 月公告，買方由光鉅控股改為台灣光罩本身，目前確認的是董事會決議與授權。台灣光罩原有業務為半導體光罩，TCK 則提供設備組裝及工程技術服務，標的位於熊本市。公告描述的是公司股權交易，沒有新增晶圓、封裝或測試產能數字。7.5 億日圓是授權上限，新台幣 1.6 億元為中央社約略換算，並非已支付對價；匯率與最終交易條件仍會影響新台幣金額。重大訊息依鉅亨轉載核對，未直接取得公開資訊觀測站原件；成交價、交割日及後續整合內容尚未公布。地點：標的所在地：日本熊本市，T.C.K Corporation；董事會決議地點未公布。</t>
+            <t xml:space="preserve">追蹤：日本核准 JASM 熊本二廠變更計畫，首階段規劃 3 奈米月產 6,000 片
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>據 Reuters 與中央社報導，日本經產省 10 月 16 日核准台積電旗下 JASM 熊本第二工廠的變更計畫，首階段規劃每月生產 6,000 片 3 奈米晶圓。新增進展是計畫獲准；3 奈米轉向已於 2 月公布，工廠仍在建設，產能數字屬規劃。JASM 為台積電在日本的製造子公司，二廠設於熊本既有廠區旁。這次核准連結晶圓製程與設備建置，並未包含新的 HBM、封裝測試或伺服器出貨資料。中央社報導新計畫預定 2028 年底投產。先前的月產 4.8 萬片規劃涵蓋不同製程與建置範圍，不能直接與首階段 3 奈米月產 6,000 片計算減產率。未直接取得經產省核准文件，產能與時程依專業報導；設備名單、良率與實際量產能力尚未公布。地點：專案地點：日本熊本縣，JASM 第二工廠，鄰近既有第一工廠。</t>
           </r>
         </is>
       </c>
@@ -807,11 +809,11 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>對供應製程電源與量測控制設備的業者而言，設備組裝及在地工程服務涉及安裝、維修與驗收支援。值得確認 TCK 的服務設備範圍、客戶授權與品質流程；股權授權仍不足以判斷是否形成新的供應關係。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="178" customHeight="1">
+          <t>對蝕刻、沉積用精密電源與量測設備業者而言，相關客戶是晶圓廠及其製程設備商。值得追問的是 3 奈米設備認證、進機與驗收時程；計畫月產能尚不足以推定設備採購量或供應商訂單。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="146" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>03</t>
@@ -826,16 +828,16 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">馬來西亞發表六項本土晶片創新，涵蓋 AI 儲存、工業 FPGA 與電源控制
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>馬來西亞 10 月 16 日在吉隆坡 AiSEM 活動發表六項本土半導體創新，涵蓋 AI 處理器、儲存、可程式邏輯與電源控制。經濟部長稱合計銷售潛力約 3 億令吉，但未說明達成期間，產品發表也未同時提供量產出貨數。The Edge 列出的六項為 SkyeChip MARS1000 AI 處理器、MaiStorage aiDAPTIV+ 儲存方案、SiliconX 工業與車用 FPGA、Infinecs 車用電源調節器、Weeroc Space 衛星電源控制晶片，以及 Alphaswift FC Mini 飛行控制器；用途分別延伸至工廠、電腦、伺服器、車用與航太。州政府英文報導引述州務大臣表示，Weeroc Space 氮化鎵電源晶片已完成第二次投片。投片、產品發表、客戶認證與量產為不同階段；3 億令吉是部長估計的合計商業潛力，未公布年度營收或已簽訂單。各產品的客戶認證、量產時間、銷售基期及合計潛力達成期間未公布；現場報導對 Grand Hyatt 與 KLCC 的場館記載有差異。地點：活動城市：馬來西亞吉隆坡。主辦日程、州政府英文與 Malay Mail 報導列 Grand Hyatt；州政府馬來文報導列 KLCC，發表場館記載不一致。</t>
+            <t xml:space="preserve">追蹤：台灣光罩改由母公司擬收購熊本 TCK，授權上限 7.5 億日圓
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>台灣光罩 10 月 16 日董事會授權董事長在 7.5 億日圓內取得日本熊本設備服務商 TCK 的全部股權，中央社換算約新台幣 1.6 億元。相較 7 月公告，買方由光鉅控股改為台灣光罩本身，目前確認的是董事會決議與授權。台灣光罩原有業務為半導體光罩，TCK 則提供設備組裝及工程技術服務，標的位於熊本市。公告描述的是公司股權交易，沒有新增晶圓、封裝或測試產能數字。7.5 億日圓是授權上限，新台幣 1.6 億元為中央社約略換算，並非已支付對價；匯率與最終交易條件仍會影響新台幣金額。重大訊息依鉅亨轉載核對，未直接取得公開資訊觀測站原件；成交價、交割日及後續整合內容尚未公布。地點：標的所在地：日本熊本市，T.C.K Corporation；董事會決議地點未公布。</t>
           </r>
         </is>
       </c>
@@ -844,11 +846,11 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>對精密電源、量測與控制設備業者而言，車用電源調節、衛星電源控制及工廠邏輯控制是具體相關應用。值得確認各項產品所處的投片、測試與客戶驗證階段；合計銷售潛力尚不能作為設備需求或訂單的依據。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="146" customHeight="1">
+          <t>對供應製程電源與量測控制設備的業者而言，設備組裝及在地工程服務涉及安裝、維修與驗收支援。值得確認 TCK 的服務設備範圍、客戶授權與品質流程；股權授權仍不足以判斷是否形成新的供應關係。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="162" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>04</t>
@@ -863,29 +865,29 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">VinMetal 與 Danieli 簽軋鋼設備合約，河靜產線規劃年產逾 70 萬噸
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>VinMetal 與義大利 Danieli 10 月 15 日在河內簽約，由 Danieli 供應越南河靜鋼軌與型鋼軋製產線的核心設備。Vingroup 公告年設計產能逾 70 萬噸，範圍包含設計、製造、供應及試運轉，尚未公布合約金額與投產日期。Danieli 負責軋製產線的核心設備與試運轉，公告並提及鋼軌精整及軌頭硬化技術。這些是鋼材由製造走向最終尺寸、性能與品質驗證的工序；公告沒有列出電源、量測或控制系統的供應商。逾 70 萬噸為這一條鋼軌與型鋼產線的年設計能力，不是整座鋼廠產能，也不是已生產或已銷售噸數。未取得同範圍前期產能，因此不計算年增率。設備交付、試運轉、客戶驗收、實際產量及合約對價尚未公布。地點：簽約地：越南河內；專案地：越南河靜省永安經濟區的 VinMetal 工廠。</t>
+            <t xml:space="preserve">鴻海擬以 1,150 億日圓取得三菱電機移動 50% 股權，預定 2027 年交割
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>鴻海與三菱電機 10 月 16 日宣布，鴻海旗下利億國際投資擬以 1,150 億日圓取得三菱電機移動 50% 股權，共同經營汽車設備業務。交易預定 2027 年 10 月 1 日完成，仍須符合主管機關核准及契約條件。三菱電機移動承接三菱電機的汽車設備事業。共同公告列出的結合範圍為電子動力系統、軟體及車輛控制，並提出在日本開發電動車平台的方向；這些屬合作內容與規劃，沒有宣告新增半導體製程或資料中心產能。協議中的企業價值為 3,200 億日圓，股權價值為 2,300 億日圓；50% 股權對價按股權價值計算為 1,150 億日圓。企業價值、全部股權價值與部分股權對價的範圍不同，金額保留原公告日圓，未自行換算成新台幣。完成交割仍以主管機關核准與契約條件滿足為前提；公告未列新增訂單、整合後產量或新工廠投產時程。地點：公告發布城市：台灣台北與日本東京；公告未指定新增工廠地點。</t>
           </r>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>對工業電源轉換與量測控制設備業者而言，軋製、精整與熱處理涉及製程控制及品質驗證。值得確認 Danieli 的設備介面、現地供電條件及驗收要求；目前缺少交付排程與分包清單，無法判斷個別設備需求。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="114" customHeight="1">
+          <t>對電源轉換與量測控制設備供應商而言，相關產品是電動動力系統、車輛控制及其測試驗證。值得追問共同平台的電氣規格、供應商認證與量產驗收界面；交易仍待核准，公告也沒有設備採購或客戶訂單資料。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="178" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>05</t>
@@ -900,16 +902,16 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">榮科通過泰國子公司購地案，工業區地點與金額待定
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>榮科 10 月 16 日公告，董事會通過由泰國子公司 LCY Technology (Thailand) 購置泰國工業區土地。公司生產 PCB 與銅箔基板用電解銅箔，但這次未公布土地賣方、價款、城市或新增產能。中央社說明榮科產品用於 PCB 與銅箔基板，連結材料、板材與電子系統供應鏈。公告只通過購地，沒有區分未來產品等級、用途或客戶，不能據此認定為新增 AI 伺服器專用產線。原始重大訊息依轉載核對；確切廠址、交易對象、土地金額、建廠與量產時程尚未公布。地點：專案國家：泰國，工業區土地；城市與園區名稱尚未公布。</t>
+            <t xml:space="preserve">鴻海等業者簽表後儲能協議，規劃 306 kWh 電池櫃與 2027 年供貨
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>鴻海與台灣儲能團隊 10 月 16 日在 Energy Taiwan 展期宣布簽署合作協議，規劃單櫃 306 kWh 的國產化表後儲能電池系統。團隊目標於 2027 年上半年完成認證及正式供貨，2027 年累計建置 100 MWh；兩項時間與規模均為目標。鴻海提供國產電芯，合作團隊包含利佳興業、盛達旗下盛齊綠能與晟瑞科技等業者，整合代工、工程與客戶服務。公司表示可供應單一電池直流櫃，或整合電力轉換系統 PCS 與能源管理系統 EMS，對應工商業儲能及需量管理。306 kWh 為單櫃規劃能量，100 MWh 為 2027 年累計市場建置目標，範圍與期間均不同。團隊預計 2026 年完成直流櫃開發，再於 2027 上半年完成認證與供貨，未提供可比較的既有安裝基數。尚未公布完成認證、正式供貨或已驗收建置實績；306 kWh 是儲存能量，公告未列 PCS 額定輸出功率，不能換作 306 kW。地點：展會場地：台灣台北南港展覽館一館；Energy Taiwan 展期為 10/14 至 10/16。新聞稿未另列簽約儀式室別。</t>
           </r>
         </is>
       </c>
@@ -918,11 +920,11 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>對製程電源與工業量測設備業者而言，銅箔工廠可能涉及電化學製程、品質量測與廠務供電，但這則公告只確認購地授權。值得追問後續產品規格、工程範圍及設備驗收條件；目前尚無可支持設備訂單判斷的建廠資料。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="130" customHeight="1">
+          <t>對電力轉換與量測控制供應商而言，相關客戶包括電池系統整合商與工商用戶，介面涉及 PCS、EMS 及現場驗收。值得核對額定功率、通訊規格與認證要求；306 kWh 與 100 MWh 分別是規格及目標，不能據以推算已下單的轉換器數量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="146" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>06</t>
@@ -937,62 +939,136 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">Genting 與華為合作規劃柔佛 430 英畝智慧園區，未披露新增投資額
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>10 月 16 日報導顯示，Genting Property 與華為馬來西亞已簽智慧城市總體規劃協議，合作範圍包含柔佛古來 430 英畝智慧園區。這次公布的是規劃合作，未披露已簽租戶、資料中心 MW 容量或新增外商投資金額。Bernama 引述公司表示，華為提供 AI 與智慧園區規劃經驗，合作亦提及農業科技與能源管理。430 英畝屬智慧園區規劃面積，沒有直接換算成資料中心機房面積或已通電容量的資料。未取得協議原文；聲明日期有一天差異，建設時程、實際投資、租戶及供電容量尚未公布。地點：專案地：馬來西亞柔佛州古來，Johor Tech Smart City；簽約活動場地：中國深圳龍崗國際藝術中心，確切簽署日未公布。</t>
+            <t xml:space="preserve">經部稱台電離岸二期累計完成 4 部風機安裝，付款與聯貸爭議仍待處理
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>經濟部 10 月 18 日表示，台電離岸二期首批三部風機已於 16 日安裝完成，累計完成四部。針對富崴與銀行團的聯貸爭議，經部稱台電監督付款的對象限分包廠商；安裝進度與最終清償安排是不同事項。經部表示，風機安裝由富崴主動請求台電接管，後續依氣候及工安條件推進。完成風機安裝並不等同已完成電氣測試、併網或商轉；公告未提供這些後續節點日期。經部稱台電在富崴與銀行團聯貸爭議中為第三人，並與銀行團溝通。這是主管機關對付款機制的說明，不能代替契約、銀行協議或法院對權利義務的認定。工程數字依中央社轉述經部聲明，未直接取得現場驗收或原始契約；併網日期、最終責任及銀行清償安排尚未確認。地點：專案：台灣台電離岸二期風場；本次說明未列具體施工海域座標。</t>
           </r>
         </is>
       </c>
       <c r="C8" s="6" t="n">
+        <v>46313</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>對工業電源與量測控制設備業者而言，相關節點包括安裝後電氣測試、控制系統驗證與併網驗收。值得確認的是驗收依據及付款機制如何適用於設備供應與分包；目前缺少原始契約與最終清償安排，不能由安裝數推定回款。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="114" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">經濟部稱年底油氣供應無虞，中油已提前展開 2027 年首季採購
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>經濟部 10 月 18 日表示，中油持續安排替代油氣來源與船期，並已提前展開 2027 年第一季採購，官方評估供應可維持至今年底。這是主管機關對燃料調度的最新說明，未公布各貨源、船次、庫存或採購價格明細。經部說明中油尋找替代油氣來源並維持儲備，台電則負責發電與供電調度。這份聲明沒有宣布新的工業電價，也沒有對單一工廠、園區或資料中心保證特定供電量。供應充足屬經濟部評估；未取得逐船採購與到港資料，也未公布可由本聲明驗證的用戶停電率或最終供電成本。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>46313</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>對工業與資料中心電源、量測控制設備業者而言，燃料調度是客戶供電環境的背景。值得核對實際場址的電網接入、供電品質與驗收條件；官方全國供應評估尚不足以判斷特定場址的可靠度或設備採購需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="178" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">馬來西亞發表六項本土晶片創新，涵蓋 AI 儲存、工業 FPGA 與電源控制
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>馬來西亞 10 月 16 日在吉隆坡 AiSEM 活動發表六項本土半導體創新，涵蓋 AI 處理器、儲存、可程式邏輯與電源控制。經濟部長稱合計銷售潛力約 3 億令吉，但未說明達成期間，產品發表也未同時提供量產出貨數。The Edge 列出的六項為 SkyeChip MARS1000 AI 處理器、MaiStorage aiDAPTIV+ 儲存方案、SiliconX 工業與車用 FPGA、Infinecs 車用電源調節器、Weeroc Space 衛星電源控制晶片，以及 Alphaswift FC Mini 飛行控制器；用途分別延伸至工廠、電腦、伺服器、車用與航太。州政府英文報導引述州務大臣表示，Weeroc Space 氮化鎵電源晶片已完成第二次投片。投片、產品發表、客戶認證與量產為不同階段；3 億令吉是部長估計的合計商業潛力，未公布年度營收或已簽訂單。各產品的客戶認證、量產時間、銷售基期及合計潛力達成期間未公布；現場報導對 Grand Hyatt 與 KLCC 的場館記載有差異。地點：活動城市：馬來西亞吉隆坡。主辦日程、州政府英文與 Malay Mail 報導列 Grand Hyatt；州政府馬來文報導列 KLCC，發表場館記載不一致。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
         <v>46311</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>對資料中心及工業電源、量測控制設備業者而言，園區能源管理是相關應用，但目前資料僅支持總體規劃合作。值得確認實際租戶、配電設計與機房容量；土地面積不能用來推算電源設備數量或採購時點。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="146" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t xml:space="preserve">越南政府提出 2027 年至少 10% 成長目標，估 2026 年貿易額達 1.11 兆美元
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>越南政府 10 月 17 日向國會提出 2027 年 GDP 成長至少 10%、CPI 約 4.5% 及勞動生產力成長 8.6% 的目標。同份報告估計 2026 年全年商品進出口達 1.11 兆美元；前者為政策目標，後者為全年估計，均非已完成實績。政府報告將製造業、配套產業、物流及能源基礎建設列為工作內容。這些是官方政策方向，尚未提供對應到特定晶圓、封測、伺服器或工廠設備的採購清單。GDP 成長、消費者物價與勞動生產力各有不同定義，不能並列解讀為同一產業成長率。1.11 兆美元在結構化資料記為 1,110 十億美元；未用四捨五入的成長率反推基期，也未將全年估計標為已公布統計實績。目標是否獲完整落實及各產業分項需求仍未知；商品進出口總額同時計入出口與進口，不能等同境內新增訂單。地點：報告發表地：越南河內，國會會議。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>46312</v>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>對工業電源、資料中心電源與量測控制設備業者而言，總體政策提供工廠及基礎建設客戶的背景。值得確認的是個別客戶已核准的工程、供電與驗收時程；GDP 目標和貿易估計無法單獨證明設備需求或採購訂單。</t>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>對精密電源、量測與控制設備業者而言，車用電源調節、衛星電源控制及工廠邏輯控制是具體相關應用。值得確認各項產品所處的投片、測試與客戶驗證階段；合計銷售潛力尚不能作為設備需求或訂單的依據。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="146" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">新加坡 9 月非石油本地出口年增 68.4%，對台出口年增 96.9%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>新加坡企業發展局 10 月 16 日公布，9 月非石油本地出口（NODX）年增 68.4%，對台灣部分年增 96.9%。電子 NODX 年增 107.6%，但整體躍升亦受船體結構產品不規則出貨及去年低基期影響，不能全歸因於 AI 晶片需求。官方報告顯示，9 月對台 NODX 的成長來源包括儲存媒體、專用機械及積體電路；後兩者對台出口年增率分別為 115.6% 與 36.2%。這些是產品類別貿易值的變動，未指定設備廠、晶圓廠或終端客戶。非電子 NODX 年增 54.2%，船體結構產品是主要貢獻項目，官方因去年基期極低而未列該項年增率。1 至 9 月 NODX 累計年增 27.6%；累計期間與單月口徑不同，不能把 9 月成長率當作全年增速。出口為名目統計，無法單獨辨識價格、數量及產品組合貢獻；專用機械未逐項列出半導體設備，亦未對應到個別客戶採購案。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>對精密電源與量測控制供應商而言，對台專用機械及 IC 出口提供跨境設備與製造活動的總體線索。值得核對的是機械子分類、價格與實體出貨量，以及客戶驗收時點；名目出口增幅與船體低基期不能直接轉成設備訂單判斷。</t>
         </is>
       </c>
     </row>

--- a/docs/exports/week-2026-10-18.xlsx
+++ b/docs/exports/week-2026-10-18.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="66" customHeight="1">
+    <row r="3" ht="82" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>01</t>
@@ -538,24 +538,24 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">越南與 EFTA 簽署協定，設備與投資規則待對照生效條件
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>越南與 EFTA 四國 10/18 在河內簽署協定，涵蓋貨品、服務、投資、原產地及政府採購。工業設備與電機是既有貿易項目，生效日期和逐項產品待遇尚不能僅由簽署公告認定。</t>
+            <t xml:space="preserve">AI 機房與伺服器建置：營運、長約與投資分層披露
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Bitdeer 10/19 新公布 9 月集團 GPU 利用率 95%，馬來西亞 A201 尚待 2027 年分階段交付；Aolani 同日公布最高 500 MW 非約束性意向書。台灣神雲約 126.2 億元新廠及擴線計畫於 10/19 公開，三案未披露彼此供應關係，規劃容量不能等同上線。</t>
           </r>
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>46313</v>
-      </c>
-    </row>
-    <row r="4" ht="66" customHeight="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="4" ht="82" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>02</t>
@@ -570,24 +570,26 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">熊本晶圓計畫核准與在地設備服務收購授權
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>據專業報導，日本 10/16 核准 JASM 二廠首階段 3 奈米計畫，台灣光罩同日改由母公司擬收購 TCK。晶圓產能仍為建置規劃，設備服務收購尚未確認交割，原始核准文件與公告取得範圍有限。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="5" ht="66" customHeight="1">
+            <t xml:space="preserve">晶圓、設備服務與先進封裝各有核准、投資及驗證節點
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>據專業報導，JASM 10/16 獲准變更熊本二廠計畫，台灣光罩同日授權擬收購 TCK，原始文件取得仍有限。10/19 宸鴻提出兩年 60 億元 TGV 規劃，力成揭露區間合計約 7.39 億元封裝設備交易；規劃、授權及採購均未等同量產或交割完成。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>10/16、10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="82" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>03</t>
@@ -602,21 +604,21 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">鴻海擬取得三菱電機移動半數股權，合作涵蓋電動動力與控制
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>10/16 協議將 50% 股權對價定為 1,150 億日圓，標的全部股權價值為 2,300 億日圓。預定 2027/10/1 交割，仍待核准及契約條件；公告未提供新增出貨或工廠產量。</t>
+            <t xml:space="preserve">PCB 泰國設備交易與台灣產學合作分別公布
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>臻鼎 10/19 揭露泰國子公司近一年設備交易約 10.86 億元，金額不是單日新增投資，原始公告依轉載核對。同日中央大學與臻鼎、台光、大量、尖點簽約，四家合計 6,000 萬元支持教學及研發，未公布新增產能或招生規模。</t>
           </r>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
@@ -634,16 +636,16 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">台灣儲能合作、燃料調度與風電工程各有不同完成節點
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>鴻海團隊 10/16 公布 306 kWh 表後儲能櫃規劃與 2027 上半年供貨目標，經部 10/18 稱中油已展開次年首季採購。離岸二期累計四部完成安裝為經部轉述，尚未等同併網，聯貸付款爭議也未有最終清償安排。</t>
+            <t xml:space="preserve">越南協定簽署與新加坡出口統計分屬制度及需求資料
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>越南與 EFTA 四國 10/18 簽署自由貿易協定，產品優惠與生效日仍待正式文本條件。新加坡 10/16 公布 9 月 NODX 年增 68.4%、對台年增 96.9%，總體增幅含船體不規則出貨與低基期，不能全歸因於 AI。</t>
           </r>
         </is>
       </c>
@@ -668,16 +670,16 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">新加坡電子外銷與馬來西亞晶片發表分屬出貨及開發資料
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>新加坡 10/16 公布 9 月 NODX 年增 68.4%、對台年增 96.9%，總體增幅包含船體低基期因素。馬來西亞同日發表六項本土晶片創新，3 億令吉銷售潛力無明確期間，發表場館記載亦有差異。</t>
+            <t xml:space="preserve">鴻海擬取得三菱電機移動半數股權，交割仍有條件
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>10/16 公布協議將 50% 股權對價定為 1,150 億日圓，合作涵蓋汽車設備業務。預定 2027/10/1 交割，須完成主管機關核准與契約條件，未披露新增訂單或工廠產量。</t>
           </r>
         </is>
       </c>
@@ -701,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -739,7 +741,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="146" customHeight="1">
+    <row r="3" ht="194" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>01</t>
@@ -754,25 +756,25 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">越南與 EFTA 四國簽署自由貿易協定，涵蓋工業品、原產地與投資規則
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>越南與瑞士、挪威、冰島、列支敦斯登 10 月 18 日在河內簽署自由貿易協定，涵蓋貨品、服務、原產地、投資及政府採購。電機與機械已是雙方貿易項目，但簽署不代表所有產品當日免稅；生效日與各產品優惠條件仍須以正式文本及附表確認。EFTA 指出，電機與機械均列於既有雙邊貨品貿易中。越南工商部列出的協定範圍包含關稅、技術性貿易障礙、海關程序及投資；公告沒有列出受惠供應商或新建產線名單。雙方 7 月 2 日結束談判，10 月 18 日完成簽署。EFTA 提供的章節說明仍為 7 月版本，列有產品別原產地規則；簽署、完成國內程序與優惠實際適用是不同階段。所閱公告未確立生效日期或逐項產品優惠時程；個別設備稅則、原產地及認證適用仍須依正式協定與附表確認。地點：簽署地點：越南河內；所閱官方公告未列具體會議場館。</t>
+            <t xml:space="preserve">Bitdeer 公布 9 月 GPU 利用率 95%，馬來西亞 A201 列分階段交付時程
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Bitdeer 於台灣時間 10 月 20 日公布 9 月未經審計營運更新，集團 AI Cloud GPU 利用率由 8 月 92% 升至 95%，已部署 GPU 維持 4,328 顆。馬來西亞柔佛新山 A201 約 21.7 MW 計畫已有逾七成長約涵蓋，仍未全面上線，機房就緒與完整部署列為不同節點。GPU 訂閱服務連結伺服器機櫃、電源轉換、液冷與機房供電。9 月外部訂閱 GPU 為 4,007 顆，8 月為 3,998 顆；這些是集團合計，不是馬來西亞單一基地數字。公司另列馬來西亞 A101 的 2.5 MW 已上線，與 A201 規劃容量分開。公司列 9 月年化收入運行率約 8,600 萬美元、收入儲備約 29 億美元，8 月分別為 8,600 萬及 9 億美元。前者按月底當日契約 GPU 收入乘 365，後者為未來合約收入，不是已認列年度營收。A201 表格列 2027 年 1 月機房就緒，正文列同年 4 月完整部署及上線目標，並稱已採購逾 100 櫃 GB300 NVL72。數字為公司未經審計更新；A201 一月機房就緒與四月全面上線的驗收定義、實際通電及收入認列時點未完整說明。地點：專案地點：馬來西亞柔佛州新山 A201 資料中心；公告另列馬來西亞 A101 已上線。</t>
           </r>
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>對精密電源與量測控制設備供應商而言，相關環節是越南工廠設備與測試產品的跨境交易。值得核對的是產品稅則、原產地與認證條件在正式生效文本中的適用；目前沒有客戶採購資料，不能由協定簽署推定新增訂單。</t>
+          <t>對資料中心電源轉換及量測業者而言，A201 的機櫃採購、液冷架構與通電驗收值得分開追問。集團利用率無法代替馬來西亞基地的負載測試，仍需確認實際上架、供電品質及客戶接受條件，不能據規劃容量推定設備需求已落實。</t>
         </is>
       </c>
     </row>
@@ -791,6 +793,80 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
+            <t xml:space="preserve">Aolani 簽馬來西亞最高 500 MW 意向書，仍待正式協議
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>新加坡 Aolani 10 月 19 日宣布，已簽意向書擬取得馬來西亞多處最高 500 MW AI 資料中心容量，目標自 2027 年下半年開始上線。公司明列意向書不具約束力，須再洽簽正式協議，未公開基地城市、供電條件或投資金額。Aolani 將提供 AI 基礎設施、GPU 部署及營運需求；機房屬設計符合 Tier III，未稱已獲認證。公司稱 2026 年已承諾容量約 80 MW，目標 2027 年合計最高 580 MW；80 MW 不是已營運容量、580 MW 也不是此次新增量。官網與 TNGlobal 日期為 10/19，ACCESS 發稿頁列 10/18 23:45、未註明時區，實際簽字日未列。意向書不具約束力；交易對手、基地、正式合約、供電核定、實際營運容量及簽署日期未公布。地點：專案地點：馬來西亞多處基地，城市及場址未公布；公告發布於新加坡。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>對資料中心電源轉換、配電量測及散熱控制業者而言，須先辨識意向容量對應的場址、業主與 GPU 營運分工。正式供電核定、機櫃規格及驗收時程均未公開，無法由 500 MW 意向推定已成立的設備需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">神雲台灣 126.2 億元投資案公開，規劃楊梅新廠及竹南、林口擴線
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>投資臺灣事務所 10 月 19 日公開神雲科技約新台幣 126.2 億元投資案，規劃在桃園楊梅新建工廠，並擴增竹南與林口既有產線，預計新增 300 名本國員工。官方原文載明 10 月 16 日核准，這次公開的是伺服器與整機櫃製造計畫，尚無完工或投產日期。神雲是神達控股旗下、以 MiTAC Computing 品牌供應資料中心及企業級伺服器的公司。官方列出從伺服器平台延伸至機櫃、AI 叢集與 OCP 架構，並研發氣冷及液冷；產線將導入 AIoT、智慧倉儲物流、自動組裝與 AI 視覺，涵蓋整機及工廠自動化。計畫另含企業 AI 算力中心、能源管理與太陽能；LEED 黃金級是爭取中的認證目標。126.2 億元是整體計畫金額，未按廠區分列，也不是當期設備支出實績。經濟日報將核准寫為 19 日，日期採官方原文的 16 日，19 日保留為公開日期。廠區別資本支出、伺服器或機櫃年產能、供電核定量與完工投產日期尚未公布。地點：專案地點：台灣桃園市楊梅區新廠；苗栗縣竹南及新北市林口既有廠區擴線。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>對機櫃電源、散熱控制與工廠量測供應商而言，三個廠區的產品分工及實際產線規格值得確認。公告還不足以判定新機櫃功率、設備驗收條件或需求時間，應將核准投資與已發包設備分開理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="146" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
             <t xml:space="preserve">追蹤：日本核准 JASM 熊本二廠變更計畫，首階段規劃 3 奈米月產 6,000 片
 </t>
           </r>
@@ -801,80 +877,6 @@
               <sz val="11"/>
             </rPr>
             <t>據 Reuters 與中央社報導，日本經產省 10 月 16 日核准台積電旗下 JASM 熊本第二工廠的變更計畫，首階段規劃每月生產 6,000 片 3 奈米晶圓。新增進展是計畫獲准；3 奈米轉向已於 2 月公布，工廠仍在建設，產能數字屬規劃。JASM 為台積電在日本的製造子公司，二廠設於熊本既有廠區旁。這次核准連結晶圓製程與設備建置，並未包含新的 HBM、封裝測試或伺服器出貨資料。中央社報導新計畫預定 2028 年底投產。先前的月產 4.8 萬片規劃涵蓋不同製程與建置範圍，不能直接與首階段 3 奈米月產 6,000 片計算減產率。未直接取得經產省核准文件，產能與時程依專業報導；設備名單、良率與實際量產能力尚未公布。地點：專案地點：日本熊本縣，JASM 第二工廠，鄰近既有第一工廠。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>46311</v>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>對蝕刻、沉積用精密電源與量測設備業者而言，相關客戶是晶圓廠及其製程設備商。值得追問的是 3 奈米設備認證、進機與驗收時程；計畫月產能尚不足以推定設備採購量或供應商訂單。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="146" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t xml:space="preserve">追蹤：台灣光罩改由母公司擬收購熊本 TCK，授權上限 7.5 億日圓
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>台灣光罩 10 月 16 日董事會授權董事長在 7.5 億日圓內取得日本熊本設備服務商 TCK 的全部股權，中央社換算約新台幣 1.6 億元。相較 7 月公告，買方由光鉅控股改為台灣光罩本身，目前確認的是董事會決議與授權。台灣光罩原有業務為半導體光罩，TCK 則提供設備組裝及工程技術服務，標的位於熊本市。公告描述的是公司股權交易，沒有新增晶圓、封裝或測試產能數字。7.5 億日圓是授權上限，新台幣 1.6 億元為中央社約略換算，並非已支付對價；匯率與最終交易條件仍會影響新台幣金額。重大訊息依鉅亨轉載核對，未直接取得公開資訊觀測站原件；成交價、交割日及後續整合內容尚未公布。地點：標的所在地：日本熊本市，T.C.K Corporation；董事會決議地點未公布。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>46311</v>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>對供應製程電源與量測控制設備的業者而言，設備組裝及在地工程服務涉及安裝、維修與驗收支援。值得確認 TCK 的服務設備範圍、客戶授權與品質流程；股權授權仍不足以判斷是否形成新的供應關係。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="162" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t xml:space="preserve">鴻海擬以 1,150 億日圓取得三菱電機移動 50% 股權，預定 2027 年交割
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>鴻海與三菱電機 10 月 16 日宣布，鴻海旗下利億國際投資擬以 1,150 億日圓取得三菱電機移動 50% 股權，共同經營汽車設備業務。交易預定 2027 年 10 月 1 日完成，仍須符合主管機關核准及契約條件。三菱電機移動承接三菱電機的汽車設備事業。共同公告列出的結合範圍為電子動力系統、軟體及車輛控制，並提出在日本開發電動車平台的方向；這些屬合作內容與規劃，沒有宣告新增半導體製程或資料中心產能。協議中的企業價值為 3,200 億日圓，股權價值為 2,300 億日圓；50% 股權對價按股權價值計算為 1,150 億日圓。企業價值、全部股權價值與部分股權對價的範圍不同，金額保留原公告日圓，未自行換算成新台幣。完成交割仍以主管機關核准與契約條件滿足為前提；公告未列新增訂單、整合後產量或新工廠投產時程。地點：公告發布城市：台灣台北與日本東京；公告未指定新增工廠地點。</t>
           </r>
         </is>
       </c>
@@ -883,11 +885,11 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>對電源轉換與量測控制設備供應商而言，相關產品是電動動力系統、車輛控制及其測試驗證。值得追問共同平台的電氣規格、供應商認證與量產驗收界面；交易仍待核准，公告也沒有設備採購或客戶訂單資料。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="178" customHeight="1">
+          <t>對蝕刻、沉積用精密電源與量測設備業者而言，相關客戶是晶圓廠及其製程設備商。值得追問的是 3 奈米設備認證、進機與驗收時程；計畫月產能尚不足以推定設備採購量或供應商訂單。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="146" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>05</t>
@@ -902,16 +904,16 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">鴻海等業者簽表後儲能協議，規劃 306 kWh 電池櫃與 2027 年供貨
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>鴻海與台灣儲能團隊 10 月 16 日在 Energy Taiwan 展期宣布簽署合作協議，規劃單櫃 306 kWh 的國產化表後儲能電池系統。團隊目標於 2027 年上半年完成認證及正式供貨，2027 年累計建置 100 MWh；兩項時間與規模均為目標。鴻海提供國產電芯，合作團隊包含利佳興業、盛達旗下盛齊綠能與晟瑞科技等業者，整合代工、工程與客戶服務。公司表示可供應單一電池直流櫃，或整合電力轉換系統 PCS 與能源管理系統 EMS，對應工商業儲能及需量管理。306 kWh 為單櫃規劃能量，100 MWh 為 2027 年累計市場建置目標，範圍與期間均不同。團隊預計 2026 年完成直流櫃開發，再於 2027 上半年完成認證與供貨，未提供可比較的既有安裝基數。尚未公布完成認證、正式供貨或已驗收建置實績；306 kWh 是儲存能量，公告未列 PCS 額定輸出功率，不能換作 306 kW。地點：展會場地：台灣台北南港展覽館一館；Energy Taiwan 展期為 10/14 至 10/16。新聞稿未另列簽約儀式室別。</t>
+            <t xml:space="preserve">追蹤：台灣光罩改由母公司擬收購熊本 TCK，授權上限 7.5 億日圓
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>台灣光罩 10 月 16 日董事會授權董事長在 7.5 億日圓內取得日本熊本設備服務商 TCK 的全部股權，中央社換算約新台幣 1.6 億元。相較 7 月公告，買方由光鉅控股改為台灣光罩本身，目前確認的是董事會決議與授權。台灣光罩原有業務為半導體光罩，TCK 則提供設備組裝及工程技術服務，標的位於熊本市。公告描述的是公司股權交易，沒有新增晶圓、封裝或測試產能數字。7.5 億日圓是授權上限，新台幣 1.6 億元為中央社約略換算，並非已支付對價；匯率與最終交易條件仍會影響新台幣金額。重大訊息依鉅亨轉載核對，未直接取得公開資訊觀測站原件；成交價、交割日及後續整合內容尚未公布。地點：標的所在地：日本熊本市，T.C.K Corporation；董事會決議地點未公布。</t>
           </r>
         </is>
       </c>
@@ -920,11 +922,11 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>對電力轉換與量測控制供應商而言，相關客戶包括電池系統整合商與工商用戶，介面涉及 PCS、EMS 及現場驗收。值得核對額定功率、通訊規格與認證要求；306 kWh 與 100 MWh 分別是規格及目標，不能據以推算已下單的轉換器數量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="146" customHeight="1">
+          <t>對供應製程電源與量測控制設備的業者而言，設備組裝及在地工程服務涉及安裝、維修與驗收支援。值得確認 TCK 的服務設備範圍、客戶授權與品質流程；股權授權仍不足以判斷是否形成新的供應關係。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="178" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>06</t>
@@ -939,136 +941,247 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">經部稱台電離岸二期累計完成 4 部風機安裝，付款與聯貸爭議仍待處理
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>經濟部 10 月 18 日表示，台電離岸二期首批三部風機已於 16 日安裝完成，累計完成四部。針對富崴與銀行團的聯貸爭議，經部稱台電監督付款的對象限分包廠商；安裝進度與最終清償安排是不同事項。經部表示，風機安裝由富崴主動請求台電接管，後續依氣候及工安條件推進。完成風機安裝並不等同已完成電氣測試、併網或商轉；公告未提供這些後續節點日期。經部稱台電在富崴與銀行團聯貸爭議中為第三人，並與銀行團溝通。這是主管機關對付款機制的說明，不能代替契約、銀行協議或法院對權利義務的認定。工程數字依中央社轉述經部聲明，未直接取得現場驗收或原始契約；併網日期、最終責任及銀行清償安排尚未確認。地點：專案：台灣台電離岸二期風場；本次說明未列具體施工海域座標。</t>
+            <t xml:space="preserve">宸鴻公布兩年 60 億元 TGV 擴建規劃，預告 300 毫米玻璃面板展品
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>宸鴻 10 月 19 日透過新聞稿表示，規劃兩年內在台灣逐步投入新台幣 60 億元，擴建玻璃通孔（TGV）廠房及產線，並預告在 TPCA Show 展出 300 × 300 毫米面板。中壢試產線正與封裝業者共同開發樣品，核心驗證以 2027 年底為目標，量產則預計 2028 年。TGV 連結玻璃基板加工、金屬填孔、電性量測及先進封裝。宸鴻稱與清華大學電資學院合作建立模型；300 毫米是方形展品的邊長，不是晶圓產能。10 月 15 日報導已提及試產線，因此新增資訊是這次投資規劃與展品細節，不是首次建成產線。主辦單位確認 TPCA Show 為 10 月 20 至 22 日、南港 1 館；IMPACT-IAAC 為 19 至 22 日、南港 2 館，兩者場館不同。兩年投入、驗證與量產日期均為公司規劃，不能當成已完成客戶認證或商用交付。未直接取得公司新聞稿原件；客戶名單、量產良率、實際支出與認證完成日期未公布，技術及時程依公司對外說法。地點：專案地點：台灣桃園中壢試產廠；展覽場地：台北南港展覽館 1 館 1、4 樓，TPCA Show 10/20 至 10/22。</t>
           </r>
         </is>
       </c>
       <c r="C8" s="6" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>對製程電源、電鍍控制及電性量測業者而言，玻璃加工、填孔與面板級驗證的設備規格值得追問。現有資訊是試產與展品，尚不能確認量產良率、客戶接受條件或設備訂單，仍需區分研發驗證與量產支出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="130" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">力成公告向 Onto 購買封裝設備，交易期間合計約 7.39 億元
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>力成 10 月 19 日公告向 Onto Innovation 取得封裝設備一批，9 月 30 日至 10 月 19 日交易金額合計新台幣 7 億 3,855 萬元。資訊來自專業媒體轉載重大訊息，確認的是設備交易，未說明交付、裝機、驗收或特定 HBM 產線。力成官方封裝服務包含記憶體與 SSD 用途；Onto 官方業務涵蓋檢測、量測及微影設備。兩家公司業務背景不等於本批設備的具體用途，公告未列型號，不能據此指認為 Dragonfly G5、HBM 或面板級封裝擴產。金額是交易區間合計，不是 10/19 單日支出，也未提供同比基期。重大訊息依 MoneyDJ 轉載核對，未直接取得公開資訊觀測站原件；設備型號、數量、設置基地、交付驗收及新增產能未公布。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>對封裝設備電源與量測供應商而言，值得確認本批設備的機型、電源介面及實際裝機計畫。供應商名稱無法界定終端製程或 HBM 曝險，現有公告也不足以推算新增設備配套需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="146" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">臻鼎泰國子公司揭露近一年設備交易，累計約 10.86 億元
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>臻鼎-KY 10 月 19 日代泰國子公司公告，向 SYMTEK AUTOMATION CHINA 取得營業用設備一批，2025 年 10 月 20 日至 2026 年 10 月 19 日累計金額約新台幣 10.86 億元。這是近一年交易期間的彙總，不是單日新增投資，也未列本批設備的驗收產能。買方為 PENG SHEN TECHNOLOGY (THAILAND)，交易金額原文為新台幣 1,085,742,322 元，付款依設備合約辦理，對方不是關係人。臻鼎的電路板業務連結材料、製程設備及終端電子組裝，但這次公告未指認設備型號或 PCB／載板產品分工，不將集團業務直接當成本批設備產出。原始重大訊息依專業資訊轉載核對；設備機型、數量、實際裝機場址、驗收、產能及資金匯入時點未公布。地點：專案地點：泰國子公司；本批設備的城市與廠址未公布。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>對工廠自動化與製程電源業者而言，應辨識這批設備的製程位置、當地服務與驗收需求。累計金額跨近一年，且沒有機型與裝機日，尚不足以判定下一期擴產或新增供應需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="130" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">中央大學與四家 PCB 業者簽約，合計 6,000 萬元推產學合作
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>中央大學 10 月 19 日在桃園與臻鼎、台光、大量及尖點簽署合作，四家合計提供新台幣 6,000 萬元，串連課程、企業專班、實習與共同研發。計畫涵蓋 PCB 材料及精密製程人才，也提出虛擬 PCB 學院構想，並非新增工廠產能公告。合作夥伴跨越電路板、銅箔基板材料與加工設備、工具，校方將整合跨領域教學及產業研究。校方新聞稿刊於中央社訊息平台，屬大學自行提供內容；中央社另有記者報導。6,000 萬元是四家合計金額，不是每家各投入相同金額，也不是已支付款項的查核結果。招生規模、各家款項分配與實際支付、課程啟動及研發成果時程未公布。地點：簽約場地：台灣桃園市中央大學羅家倫講堂。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>對製程電源、精密控制及量測供應商而言，合作課程是否涵蓋材料測試、加工控制及設備驗證值得了解。現階段沒有招生與研發成果時程，不能由合作金額推定可用人力或量產技術已形成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="146" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">越南與 EFTA 四國簽署自由貿易協定，涵蓋工業品、原產地與投資規則
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>越南與瑞士、挪威、冰島、列支敦斯登 10 月 18 日在河內簽署自由貿易協定，涵蓋貨品、服務、原產地、投資及政府採購。電機與機械已是雙方貿易項目，但簽署不代表所有產品當日免稅；生效日與各產品優惠條件仍須以正式文本及附表確認。EFTA 指出，電機與機械均列於既有雙邊貨品貿易中。越南工商部列出的協定範圍包含關稅、技術性貿易障礙、海關程序及投資；公告沒有列出受惠供應商或新建產線名單。雙方 7 月 2 日結束談判，10 月 18 日完成簽署。EFTA 提供的章節說明仍為 7 月版本，列有產品別原產地規則；簽署、完成國內程序與優惠實際適用是不同階段。所閱公告未確立生效日期或逐項產品優惠時程；個別設備稅則、原產地及認證適用仍須依正式協定與附表確認。地點：簽署地點：越南河內；所閱官方公告未列具體會議場館。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
         <v>46313</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>對工業電源與量測控制設備業者而言，相關節點包括安裝後電氣測試、控制系統驗證與併網驗收。值得確認的是驗收依據及付款機制如何適用於設備供應與分包；目前缺少原始契約與最終清償安排，不能由安裝數推定回款。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="114" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t xml:space="preserve">經濟部稱年底油氣供應無虞，中油已提前展開 2027 年首季採購
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>經濟部 10 月 18 日表示，中油持續安排替代油氣來源與船期，並已提前展開 2027 年第一季採購，官方評估供應可維持至今年底。這是主管機關對燃料調度的最新說明，未公布各貨源、船次、庫存或採購價格明細。經部說明中油尋找替代油氣來源並維持儲備，台電則負責發電與供電調度。這份聲明沒有宣布新的工業電價，也沒有對單一工廠、園區或資料中心保證特定供電量。供應充足屬經濟部評估；未取得逐船採購與到港資料，也未公布可由本聲明驗證的用戶停電率或最終供電成本。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>46313</v>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>對工業與資料中心電源、量測控制設備業者而言，燃料調度是客戶供電環境的背景。值得核對實際場址的電網接入、供電品質與驗收條件；官方全國供應評估尚不足以判斷特定場址的可靠度或設備採購需求。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="178" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t xml:space="preserve">馬來西亞發表六項本土晶片創新，涵蓋 AI 儲存、工業 FPGA 與電源控制
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>馬來西亞 10 月 16 日在吉隆坡 AiSEM 活動發表六項本土半導體創新，涵蓋 AI 處理器、儲存、可程式邏輯與電源控制。經濟部長稱合計銷售潛力約 3 億令吉，但未說明達成期間，產品發表也未同時提供量產出貨數。The Edge 列出的六項為 SkyeChip MARS1000 AI 處理器、MaiStorage aiDAPTIV+ 儲存方案、SiliconX 工業與車用 FPGA、Infinecs 車用電源調節器、Weeroc Space 衛星電源控制晶片，以及 Alphaswift FC Mini 飛行控制器；用途分別延伸至工廠、電腦、伺服器、車用與航太。州政府英文報導引述州務大臣表示，Weeroc Space 氮化鎵電源晶片已完成第二次投片。投片、產品發表、客戶認證與量產為不同階段；3 億令吉是部長估計的合計商業潛力，未公布年度營收或已簽訂單。各產品的客戶認證、量產時間、銷售基期及合計潛力達成期間未公布；現場報導對 Grand Hyatt 與 KLCC 的場館記載有差異。地點：活動城市：馬來西亞吉隆坡。主辦日程、州政府英文與 Malay Mail 報導列 Grand Hyatt；州政府馬來文報導列 KLCC，發表場館記載不一致。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>對精密電源與量測控制設備供應商而言，相關環節是越南工廠設備與測試產品的跨境交易。值得核對的是產品稅則、原產地與認證條件在正式生效文本中的適用；目前沒有客戶採購資料，不能由協定簽署推定新增訂單。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="146" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">新加坡 9 月非石油本地出口年增 68.4%，對台出口年增 96.9%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>新加坡企業發展局 10 月 16 日公布，9 月非石油本地出口（NODX）年增 68.4%，對台灣部分年增 96.9%。電子 NODX 年增 107.6%，但整體躍升亦受船體結構產品不規則出貨及去年低基期影響，不能全歸因於 AI 晶片需求。官方報告顯示，9 月對台 NODX 的成長來源包括儲存媒體、專用機械及積體電路；後兩者對台出口年增率分別為 115.6% 與 36.2%。這些是產品類別貿易值的變動，未指定設備廠、晶圓廠或終端客戶。非電子 NODX 年增 54.2%，船體結構產品是主要貢獻項目，官方因去年基期極低而未列該項年增率。1 至 9 月 NODX 累計年增 27.6%；累計期間與單月口徑不同，不能把 9 月成長率當作全年增速。出口為名目統計，無法單獨辨識價格、數量及產品組合貢獻；專用機械未逐項列出半導體設備，亦未對應到個別客戶採購案。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
         <v>46311</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>對精密電源、量測與控制設備業者而言，車用電源調節、衛星電源控制及工廠邏輯控制是具體相關應用。值得確認各項產品所處的投片、測試與客戶驗證階段；合計銷售潛力尚不能作為設備需求或訂單的依據。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="146" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t xml:space="preserve">新加坡 9 月非石油本地出口年增 68.4%，對台出口年增 96.9%
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>新加坡企業發展局 10 月 16 日公布，9 月非石油本地出口（NODX）年增 68.4%，對台灣部分年增 96.9%。電子 NODX 年增 107.6%，但整體躍升亦受船體結構產品不規則出貨及去年低基期影響，不能全歸因於 AI 晶片需求。官方報告顯示，9 月對台 NODX 的成長來源包括儲存媒體、專用機械及積體電路；後兩者對台出口年增率分別為 115.6% 與 36.2%。這些是產品類別貿易值的變動，未指定設備廠、晶圓廠或終端客戶。非電子 NODX 年增 54.2%，船體結構產品是主要貢獻項目，官方因去年基期極低而未列該項年增率。1 至 9 月 NODX 累計年增 27.6%；累計期間與單月口徑不同，不能把 9 月成長率當作全年增速。出口為名目統計，無法單獨辨識價格、數量及產品組合貢獻；專用機械未逐項列出半導體設備，亦未對應到個別客戶採購案。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>對精密電源與量測控制供應商而言，對台專用機械及 IC 出口提供跨境設備與製造活動的總體線索。值得核對的是機械子分類、價格與實體出貨量，以及客戶驗收時點；名目出口增幅與船體低基期不能直接轉成設備訂單判斷。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="162" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">鴻海擬以 1,150 億日圓取得三菱電機移動 50% 股權，預定 2027 年交割
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>鴻海與三菱電機 10 月 16 日宣布，鴻海旗下利億國際投資擬以 1,150 億日圓取得三菱電機移動 50% 股權，共同經營汽車設備業務。交易預定 2027 年 10 月 1 日完成，仍須符合主管機關核准及契約條件。三菱電機移動承接三菱電機的汽車設備事業。共同公告列出的結合範圍為電子動力系統、軟體及車輛控制，並提出在日本開發電動車平台的方向；這些屬合作內容與規劃，沒有宣告新增半導體製程或資料中心產能。協議中的企業價值為 3,200 億日圓，股權價值為 2,300 億日圓；50% 股權對價按股權價值計算為 1,150 億日圓。企業價值、全部股權價值與部分股權對價的範圍不同，金額保留原公告日圓，未自行換算成新台幣。完成交割仍以主管機關核准與契約條件滿足為前提；公告未列新增訂單、整合後產量或新工廠投產時程。地點：公告發布城市：台灣台北與日本東京；公告未指定新增工廠地點。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
         <v>46311</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>對精密電源與量測控制供應商而言，對台專用機械及 IC 出口提供跨境設備與製造活動的總體線索。值得核對的是機械子分類、價格與實體出貨量，以及客戶驗收時點；名目出口增幅與船體低基期不能直接轉成設備訂單判斷。</t>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>對電源轉換與量測控制設備供應商而言，相關產品是電動動力系統、車輛控制及其測試驗證。值得追問共同平台的電氣規格、供應商認證與量產驗收界面；交易仍待核准，公告也沒有設備採購或客戶訂單資料。</t>
         </is>
       </c>
     </row>

--- a/docs/exports/week-2026-10-18.xlsx
+++ b/docs/exports/week-2026-10-18.xlsx
@@ -21,8 +21,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="m/d"/>
+    <numFmt numFmtId="164" formatCode="m/d"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -119,7 +119,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -551,8 +551,10 @@
           </r>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
-        <v>46314</v>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>10/19、10/20</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="82" customHeight="1">
@@ -703,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -852,7 +854,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="146" customHeight="1">
+    <row r="6" ht="178" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>04</t>
@@ -867,25 +869,25 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">追蹤：日本核准 JASM 熊本二廠變更計畫，首階段規劃 3 奈米月產 6,000 片
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>據 Reuters 與中央社報導，日本經產省 10 月 16 日核准台積電旗下 JASM 熊本第二工廠的變更計畫，首階段規劃每月生產 6,000 片 3 奈米晶圓。新增進展是計畫獲准；3 奈米轉向已於 2 月公布，工廠仍在建設，產能數字屬規劃。JASM 為台積電在日本的製造子公司，二廠設於熊本既有廠區旁。這次核准連結晶圓製程與設備建置，並未包含新的 HBM、封裝測試或伺服器出貨資料。中央社報導新計畫預定 2028 年底投產。先前的月產 4.8 萬片規劃涵蓋不同製程與建置範圍，不能直接與首階段 3 奈米月產 6,000 片計算減產率。未直接取得經產省核准文件，產能與時程依專業報導；設備名單、良率與實際量產能力尚未公布。地點：專案地點：日本熊本縣，JASM 第二工廠，鄰近既有第一工廠。</t>
+            <t xml:space="preserve">馬來西亞 AI 機房相關長約與交付節點仍須分開看待
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Bitdeer 在馬來西亞的 A201 規劃仍以 2027 年 1 月機房就緒、4 月全面上線為不同節點，而 Aolani 也只揭露最高 500 MW 的非約束性意向書。兩家案子都顯示 AI 機房以長約、機房進度與供電完成度各自衡量，不能把計畫性容量直接當成已部署容量。AI 機房的關鍵節點涵蓋 GPU、伺服器機櫃、液冷和機房供電；公司更新中同時列出已上線 A101、規劃中 A201、集團 GPU 利用率和未來合約收入。這些數字屬不同層次：有的是當前已部署，另有的仍係規劃與長約。Bitdeer 披露 9 月 GPU 利用率 95%，但該值不能直接等同於 A201 的每月實際出力；A201 的階段交付仍分機房就緒與完整部署。Aolani 則列最高 500 MW 的非約束性 LOI，意思是未定義客戶最終落地與供電時間表。目前公開資料未完整說明 A201 交付條件、哪一批客戶已實際承租，以及機房通電與營收認列之間的落差。這些都仍須以正式交付公告、供電說明與長約條款為準。地點：馬來西亞柔佛州新山；A201、A101 兩處資料中心分別列示。</t>
           </r>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>對蝕刻、沉積用精密電源與量測設備業者而言，相關客戶是晶圓廠及其製程設備商。值得追問的是 3 奈米設備認證、進機與驗收時程；計畫月產能尚不足以推定設備採購量或供應商訂單。</t>
+          <t>對精密電源與量測設備業者而言，重點不是單一數字，而是機房是否能順利交付、通電與驗證。若客戶承租與供電節點仍未落地，設備採購節奏會被延後，這些資訊仍需要與長約條款一併核對。</t>
         </is>
       </c>
     </row>
@@ -904,16 +906,16 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">追蹤：台灣光罩改由母公司擬收購熊本 TCK，授權上限 7.5 億日圓
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>台灣光罩 10 月 16 日董事會授權董事長在 7.5 億日圓內取得日本熊本設備服務商 TCK 的全部股權，中央社換算約新台幣 1.6 億元。相較 7 月公告，買方由光鉅控股改為台灣光罩本身，目前確認的是董事會決議與授權。台灣光罩原有業務為半導體光罩，TCK 則提供設備組裝及工程技術服務，標的位於熊本市。公告描述的是公司股權交易，沒有新增晶圓、封裝或測試產能數字。7.5 億日圓是授權上限，新台幣 1.6 億元為中央社約略換算，並非已支付對價；匯率與最終交易條件仍會影響新台幣金額。重大訊息依鉅亨轉載核對，未直接取得公開資訊觀測站原件；成交價、交割日及後續整合內容尚未公布。地點：標的所在地：日本熊本市，T.C.K Corporation；董事會決議地點未公布。</t>
+            <t xml:space="preserve">追蹤：日本核准 JASM 熊本二廠變更計畫，首階段規劃 3 奈米月產 6,000 片
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>據 Reuters 與中央社報導，日本經產省 10 月 16 日核准台積電旗下 JASM 熊本第二工廠的變更計畫，首階段規劃每月生產 6,000 片 3 奈米晶圓。新增進展是計畫獲准；3 奈米轉向已於 2 月公布，工廠仍在建設，產能數字屬規劃。JASM 為台積電在日本的製造子公司，二廠設於熊本既有廠區旁。這次核准連結晶圓製程與設備建置，並未包含新的 HBM、封裝測試或伺服器出貨資料。中央社報導新計畫預定 2028 年底投產。先前的月產 4.8 萬片規劃涵蓋不同製程與建置範圍，不能直接與首階段 3 奈米月產 6,000 片計算減產率。未直接取得經產省核准文件，產能與時程依專業報導；設備名單、良率與實際量產能力尚未公布。地點：專案地點：日本熊本縣，JASM 第二工廠，鄰近既有第一工廠。</t>
           </r>
         </is>
       </c>
@@ -922,17 +924,54 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
+          <t>對蝕刻、沉積用精密電源與量測設備業者而言，相關客戶是晶圓廠及其製程設備商。值得追問的是 3 奈米設備認證、進機與驗收時程；計畫月產能尚不足以推定設備採購量或供應商訂單。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="146" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">追蹤：台灣光罩改由母公司擬收購熊本 TCK，授權上限 7.5 億日圓
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>台灣光罩 10 月 16 日董事會授權董事長在 7.5 億日圓內取得日本熊本設備服務商 TCK 的全部股權，中央社換算約新台幣 1.6 億元。相較 7 月公告，買方由光鉅控股改為台灣光罩本身，目前確認的是董事會決議與授權。台灣光罩原有業務為半導體光罩，TCK 則提供設備組裝及工程技術服務，標的位於熊本市。公告描述的是公司股權交易，沒有新增晶圓、封裝或測試產能數字。7.5 億日圓是授權上限，新台幣 1.6 億元為中央社約略換算，並非已支付對價；匯率與最終交易條件仍會影響新台幣金額。重大訊息依鉅亨轉載核對，未直接取得公開資訊觀測站原件；成交價、交割日及後續整合內容尚未公布。地點：標的所在地：日本熊本市，T.C.K Corporation；董事會決議地點未公布。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
           <t>對供應製程電源與量測控制設備的業者而言，設備組裝及在地工程服務涉及安裝、維修與驗收支援。值得確認 TCK 的服務設備範圍、客戶授權與品質流程；股權授權仍不足以判斷是否形成新的供應關係。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="178" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
+    <row r="9" ht="178" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -951,43 +990,6 @@
               <sz val="11"/>
             </rPr>
             <t>宸鴻 10 月 19 日透過新聞稿表示，規劃兩年內在台灣逐步投入新台幣 60 億元，擴建玻璃通孔（TGV）廠房及產線，並預告在 TPCA Show 展出 300 × 300 毫米面板。中壢試產線正與封裝業者共同開發樣品，核心驗證以 2027 年底為目標，量產則預計 2028 年。TGV 連結玻璃基板加工、金屬填孔、電性量測及先進封裝。宸鴻稱與清華大學電資學院合作建立模型；300 毫米是方形展品的邊長，不是晶圓產能。10 月 15 日報導已提及試產線，因此新增資訊是這次投資規劃與展品細節，不是首次建成產線。主辦單位確認 TPCA Show 為 10 月 20 至 22 日、南港 1 館；IMPACT-IAAC 為 19 至 22 日、南港 2 館，兩者場館不同。兩年投入、驗證與量產日期均為公司規劃，不能當成已完成客戶認證或商用交付。未直接取得公司新聞稿原件；客戶名單、量產良率、實際支出與認證完成日期未公布，技術及時程依公司對外說法。地點：專案地點：台灣桃園中壢試產廠；展覽場地：台北南港展覽館 1 館 1、4 樓，TPCA Show 10/20 至 10/22。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>46314</v>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>對製程電源、電鍍控制及電性量測業者而言，玻璃加工、填孔與面板級驗證的設備規格值得追問。現有資訊是試產與展品，尚不能確認量產良率、客戶接受條件或設備訂單，仍需區分研發驗證與量產支出。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="130" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t xml:space="preserve">力成公告向 Onto 購買封裝設備，交易期間合計約 7.39 億元
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>力成 10 月 19 日公告向 Onto Innovation 取得封裝設備一批，9 月 30 日至 10 月 19 日交易金額合計新台幣 7 億 3,855 萬元。資訊來自專業媒體轉載重大訊息，確認的是設備交易，未說明交付、裝機、驗收或特定 HBM 產線。力成官方封裝服務包含記憶體與 SSD 用途；Onto 官方業務涵蓋檢測、量測及微影設備。兩家公司業務背景不等於本批設備的具體用途，公告未列型號，不能據此指認為 Dragonfly G5、HBM 或面板級封裝擴產。金額是交易區間合計，不是 10/19 單日支出，也未提供同比基期。重大訊息依 MoneyDJ 轉載核對，未直接取得公開資訊觀測站原件；設備型號、數量、設置基地、交付驗收及新增產能未公布。</t>
           </r>
         </is>
       </c>
@@ -996,11 +998,11 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>對封裝設備電源與量測供應商而言，值得確認本批設備的機型、電源介面及實際裝機計畫。供應商名稱無法界定終端製程或 HBM 曝險，現有公告也不足以推算新增設備配套需求。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="146" customHeight="1">
+          <t>對製程電源、電鍍控制及電性量測業者而言，玻璃加工、填孔與面板級驗證的設備規格值得追問。現有資訊是試產與展品，尚不能確認量產良率、客戶接受條件或設備訂單，仍需區分研發驗證與量產支出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="130" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>08</t>
@@ -1015,16 +1017,16 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">臻鼎泰國子公司揭露近一年設備交易，累計約 10.86 億元
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>臻鼎-KY 10 月 19 日代泰國子公司公告，向 SYMTEK AUTOMATION CHINA 取得營業用設備一批，2025 年 10 月 20 日至 2026 年 10 月 19 日累計金額約新台幣 10.86 億元。這是近一年交易期間的彙總，不是單日新增投資，也未列本批設備的驗收產能。買方為 PENG SHEN TECHNOLOGY (THAILAND)，交易金額原文為新台幣 1,085,742,322 元，付款依設備合約辦理，對方不是關係人。臻鼎的電路板業務連結材料、製程設備及終端電子組裝，但這次公告未指認設備型號或 PCB／載板產品分工，不將集團業務直接當成本批設備產出。原始重大訊息依專業資訊轉載核對；設備機型、數量、實際裝機場址、驗收、產能及資金匯入時點未公布。地點：專案地點：泰國子公司；本批設備的城市與廠址未公布。</t>
+            <t xml:space="preserve">力成公告向 Onto 購買封裝設備，交易期間合計約 7.39 億元
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>力成 10 月 19 日公告向 Onto Innovation 取得封裝設備一批，9 月 30 日至 10 月 19 日交易金額合計新台幣 7 億 3,855 萬元。資訊來自專業媒體轉載重大訊息，確認的是設備交易，未說明交付、裝機、驗收或特定 HBM 產線。力成官方封裝服務包含記憶體與 SSD 用途；Onto 官方業務涵蓋檢測、量測及微影設備。兩家公司業務背景不等於本批設備的具體用途，公告未列型號，不能據此指認為 Dragonfly G5、HBM 或面板級封裝擴產。金額是交易區間合計，不是 10/19 單日支出，也未提供同比基期。重大訊息依 MoneyDJ 轉載核對，未直接取得公開資訊觀測站原件；設備型號、數量、設置基地、交付驗收及新增產能未公布。</t>
           </r>
         </is>
       </c>
@@ -1033,11 +1035,11 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>對工廠自動化與製程電源業者而言，應辨識這批設備的製程位置、當地服務與驗收需求。累計金額跨近一年，且沒有機型與裝機日，尚不足以判定下一期擴產或新增供應需求。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="130" customHeight="1">
+          <t>對封裝設備電源與量測供應商而言，值得確認本批設備的機型、電源介面及實際裝機計畫。供應商名稱無法界定終端製程或 HBM 曝險，現有公告也不足以推算新增設備配套需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="146" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>09</t>
@@ -1052,16 +1054,16 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">中央大學與四家 PCB 業者簽約，合計 6,000 萬元推產學合作
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>中央大學 10 月 19 日在桃園與臻鼎、台光、大量及尖點簽署合作，四家合計提供新台幣 6,000 萬元，串連課程、企業專班、實習與共同研發。計畫涵蓋 PCB 材料及精密製程人才，也提出虛擬 PCB 學院構想，並非新增工廠產能公告。合作夥伴跨越電路板、銅箔基板材料與加工設備、工具，校方將整合跨領域教學及產業研究。校方新聞稿刊於中央社訊息平台，屬大學自行提供內容；中央社另有記者報導。6,000 萬元是四家合計金額，不是每家各投入相同金額，也不是已支付款項的查核結果。招生規模、各家款項分配與實際支付、課程啟動及研發成果時程未公布。地點：簽約場地：台灣桃園市中央大學羅家倫講堂。</t>
+            <t xml:space="preserve">臻鼎泰國子公司揭露近一年設備交易，累計約 10.86 億元
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>臻鼎-KY 10 月 19 日代泰國子公司公告，向 SYMTEK AUTOMATION CHINA 取得營業用設備一批，2025 年 10 月 20 日至 2026 年 10 月 19 日累計金額約新台幣 10.86 億元。這是近一年交易期間的彙總，不是單日新增投資，也未列本批設備的驗收產能。買方為 PENG SHEN TECHNOLOGY (THAILAND)，交易金額原文為新台幣 1,085,742,322 元，付款依設備合約辦理，對方不是關係人。臻鼎的電路板業務連結材料、製程設備及終端電子組裝，但這次公告未指認設備型號或 PCB／載板產品分工，不將集團業務直接當成本批設備產出。原始重大訊息依專業資訊轉載核對；設備機型、數量、實際裝機場址、驗收、產能及資金匯入時點未公布。地點：專案地點：泰國子公司；本批設備的城市與廠址未公布。</t>
           </r>
         </is>
       </c>
@@ -1070,44 +1072,44 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
+          <t>對工廠自動化與製程電源業者而言，應辨識這批設備的製程位置、當地服務與驗收需求。累計金額跨近一年，且沒有機型與裝機日，尚不足以判定下一期擴產或新增供應需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="130" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">中央大學與四家 PCB 業者簽約，合計 6,000 萬元推產學合作
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>中央大學 10 月 19 日在桃園與臻鼎、台光、大量及尖點簽署合作，四家合計提供新台幣 6,000 萬元，串連課程、企業專班、實習與共同研發。計畫涵蓋 PCB 材料及精密製程人才，也提出虛擬 PCB 學院構想，並非新增工廠產能公告。合作夥伴跨越電路板、銅箔基板材料與加工設備、工具，校方將整合跨領域教學及產業研究。校方新聞稿刊於中央社訊息平台，屬大學自行提供內容；中央社另有記者報導。6,000 萬元是四家合計金額，不是每家各投入相同金額，也不是已支付款項的查核結果。招生規模、各家款項分配與實際支付、課程啟動及研發成果時程未公布。地點：簽約場地：台灣桃園市中央大學羅家倫講堂。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
           <t>對製程電源、精密控制及量測供應商而言，合作課程是否涵蓋材料測試、加工控制及設備驗證值得了解。現階段沒有招生與研發成果時程，不能由合作金額推定可用人力或量產技術已形成。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="146" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t xml:space="preserve">越南與 EFTA 四國簽署自由貿易協定，涵蓋工業品、原產地與投資規則
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>越南與瑞士、挪威、冰島、列支敦斯登 10 月 18 日在河內簽署自由貿易協定，涵蓋貨品、服務、原產地、投資及政府採購。電機與機械已是雙方貿易項目，但簽署不代表所有產品當日免稅；生效日與各產品優惠條件仍須以正式文本及附表確認。EFTA 指出，電機與機械均列於既有雙邊貨品貿易中。越南工商部列出的協定範圍包含關稅、技術性貿易障礙、海關程序及投資；公告沒有列出受惠供應商或新建產線名單。雙方 7 月 2 日結束談判，10 月 18 日完成簽署。EFTA 提供的章節說明仍為 7 月版本，列有產品別原產地規則；簽署、完成國內程序與優惠實際適用是不同階段。所閱公告未確立生效日期或逐項產品優惠時程；個別設備稅則、原產地及認證適用仍須依正式協定與附表確認。地點：簽署地點：越南河內；所閱官方公告未列具體會議場館。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>46313</v>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>對精密電源與量測控制設備供應商而言，相關環節是越南工廠設備與測試產品的跨境交易。值得核對的是產品稅則、原產地與認證條件在正式生效文本中的適用；目前沒有客戶採購資料，不能由協定簽署推定新增訂單。</t>
         </is>
       </c>
     </row>
@@ -1126,6 +1128,43 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
+            <t xml:space="preserve">越南與 EFTA 四國簽署自由貿易協定，涵蓋工業品、原產地與投資規則
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>越南與瑞士、挪威、冰島、列支敦斯登 10 月 18 日在河內簽署自由貿易協定，涵蓋貨品、服務、原產地、投資及政府採購。電機與機械已是雙方貿易項目，但簽署不代表所有產品當日免稅；生效日與各產品優惠條件仍須以正式文本及附表確認。EFTA 指出，電機與機械均列於既有雙邊貨品貿易中。越南工商部列出的協定範圍包含關稅、技術性貿易障礙、海關程序及投資；公告沒有列出受惠供應商或新建產線名單。雙方 7 月 2 日結束談判，10 月 18 日完成簽署。EFTA 提供的章節說明仍為 7 月版本，列有產品別原產地規則；簽署、完成國內程序與優惠實際適用是不同階段。所閱公告未確立生效日期或逐項產品優惠時程；個別設備稅則、原產地及認證適用仍須依正式協定與附表確認。地點：簽署地點：越南河內；所閱官方公告未列具體會議場館。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>46313</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>對精密電源與量測控制設備供應商而言，相關環節是越南工廠設備與測試產品的跨境交易。值得核對的是產品稅則、原產地與認證條件在正式生效文本中的適用；目前沒有客戶採購資料，不能由協定簽署推定新增訂單。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="146" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
             <t xml:space="preserve">新加坡 9 月非石油本地出口年增 68.4%，對台出口年增 96.9%
 </t>
           </r>
@@ -1136,43 +1175,6 @@
               <sz val="11"/>
             </rPr>
             <t>新加坡企業發展局 10 月 16 日公布，9 月非石油本地出口（NODX）年增 68.4%，對台灣部分年增 96.9%。電子 NODX 年增 107.6%，但整體躍升亦受船體結構產品不規則出貨及去年低基期影響，不能全歸因於 AI 晶片需求。官方報告顯示，9 月對台 NODX 的成長來源包括儲存媒體、專用機械及積體電路；後兩者對台出口年增率分別為 115.6% 與 36.2%。這些是產品類別貿易值的變動，未指定設備廠、晶圓廠或終端客戶。非電子 NODX 年增 54.2%，船體結構產品是主要貢獻項目，官方因去年基期極低而未列該項年增率。1 至 9 月 NODX 累計年增 27.6%；累計期間與單月口徑不同，不能把 9 月成長率當作全年增速。出口為名目統計，無法單獨辨識價格、數量及產品組合貢獻；專用機械未逐項列出半導體設備，亦未對應到個別客戶採購案。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>46311</v>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>對精密電源與量測控制供應商而言，對台專用機械及 IC 出口提供跨境設備與製造活動的總體線索。值得核對的是機械子分類、價格與實體出貨量，以及客戶驗收時點；名目出口增幅與船體低基期不能直接轉成設備訂單判斷。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="162" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <b val="1"/>
-              <color rgb="0014322B"/>
-              <sz val="13"/>
-            </rPr>
-            <t xml:space="preserve">鴻海擬以 1,150 億日圓取得三菱電機移動 50% 股權，預定 2027 年交割
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>鴻海與三菱電機 10 月 16 日宣布，鴻海旗下利億國際投資擬以 1,150 億日圓取得三菱電機移動 50% 股權，共同經營汽車設備業務。交易預定 2027 年 10 月 1 日完成，仍須符合主管機關核准及契約條件。三菱電機移動承接三菱電機的汽車設備事業。共同公告列出的結合範圍為電子動力系統、軟體及車輛控制，並提出在日本開發電動車平台的方向；這些屬合作內容與規劃，沒有宣告新增半導體製程或資料中心產能。協議中的企業價值為 3,200 億日圓，股權價值為 2,300 億日圓；50% 股權對價按股權價值計算為 1,150 億日圓。企業價值、全部股權價值與部分股權對價的範圍不同，金額保留原公告日圓，未自行換算成新台幣。完成交割仍以主管機關核准與契約條件滿足為前提；公告未列新增訂單、整合後產量或新工廠投產時程。地點：公告發布城市：台灣台北與日本東京；公告未指定新增工廠地點。</t>
           </r>
         </is>
       </c>
@@ -1180,6 +1182,43 @@
         <v>46311</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>對精密電源與量測控制供應商而言，對台專用機械及 IC 出口提供跨境設備與製造活動的總體線索。值得核對的是機械子分類、價格與實體出貨量，以及客戶驗收時點；名目出口增幅與船體低基期不能直接轉成設備訂單判斷。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="162" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <b val="1"/>
+              <color rgb="0014322B"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">鴻海擬以 1,150 億日圓取得三菱電機移動 50% 股權，預定 2027 年交割
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>鴻海與三菱電機 10 月 16 日宣布，鴻海旗下利億國際投資擬以 1,150 億日圓取得三菱電機移動 50% 股權，共同經營汽車設備業務。交易預定 2027 年 10 月 1 日完成，仍須符合主管機關核准及契約條件。三菱電機移動承接三菱電機的汽車設備事業。共同公告列出的結合範圍為電子動力系統、軟體及車輛控制，並提出在日本開發電動車平台的方向；這些屬合作內容與規劃，沒有宣告新增半導體製程或資料中心產能。協議中的企業價值為 3,200 億日圓，股權價值為 2,300 億日圓；50% 股權對價按股權價值計算為 1,150 億日圓。企業價值、全部股權價值與部分股權對價的範圍不同，金額保留原公告日圓，未自行換算成新台幣。完成交割仍以主管機關核准與契約條件滿足為前提；公告未列新增訂單、整合後產量或新工廠投產時程。地點：公告發布城市：台灣台北與日本東京；公告未指定新增工廠地點。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>對電源轉換與量測控制設備供應商而言，相關產品是電動動力系統、車輛控制及其測試驗證。值得追問共同平台的電氣規格、供應商認證與量產驗收界面；交易仍待核准，公告也沒有設備採購或客戶訂單資料。</t>
         </is>

--- a/docs/exports/week-2026-10-18.xlsx
+++ b/docs/exports/week-2026-10-18.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>10/19、10/20</t>
+          <t>10/19、10/21</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="178" customHeight="1">
+    <row r="6" ht="162" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>04</t>
@@ -869,25 +869,25 @@
               <color rgb="0014322B"/>
               <sz val="13"/>
             </rPr>
-            <t xml:space="preserve">馬來西亞 AI 機房相關長約與交付節點仍須分開看待
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="PingFang TC"/>
-              <color rgb="003B4A44"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Bitdeer 在馬來西亞的 A201 規劃仍以 2027 年 1 月機房就緒、4 月全面上線為不同節點，而 Aolani 也只揭露最高 500 MW 的非約束性意向書。兩家案子都顯示 AI 機房以長約、機房進度與供電完成度各自衡量，不能把計畫性容量直接當成已部署容量。AI 機房的關鍵節點涵蓋 GPU、伺服器機櫃、液冷和機房供電；公司更新中同時列出已上線 A101、規劃中 A201、集團 GPU 利用率和未來合約收入。這些數字屬不同層次：有的是當前已部署，另有的仍係規劃與長約。Bitdeer 披露 9 月 GPU 利用率 95%，但該值不能直接等同於 A201 的每月實際出力；A201 的階段交付仍分機房就緒與完整部署。Aolani 則列最高 500 MW 的非約束性 LOI，意思是未定義客戶最終落地與供電時間表。目前公開資料未完整說明 A201 交付條件、哪一批客戶已實際承租，以及機房通電與營收認列之間的落差。這些都仍須以正式交付公告、供電說明與長約條款為準。地點：馬來西亞柔佛州新山；A201、A101 兩處資料中心分別列示。</t>
+            <t xml:space="preserve">馬來西亞核准 27 件資料中心計畫、金額約 554 億美元
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="PingFang TC"/>
+              <color rgb="003B4A44"/>
+              <sz val="11"/>
+            </rPr>
+            <t>10/21 檢視的區域報導指出，馬來西亞新增核准 27 件資料中心計畫，合計約 554 億美元。這組數字反映的是核准與投資承諾規模，不等同同日已完成接電、機櫃上架與商轉；對供應鏈而言，仍須看實際土建、變電與租戶導入節奏。資料中心核准案會連動伺服器機櫃、配電、散熱、建廠與長週期電力設備需求。對台灣與東南亞鏈條的意義在於，新增核准會先轉化為工程與設備拉貨窗口，之後才是租戶實際裝機與營運收入。「27 件、554 億美元」是專案核准與總投資規模，不是可直接換算為當前上線 MW。若要評估短期影響，仍需拆開看土地取得、電力接入進度、機電建置與客戶簽約成熟度。公開報導未完整列出每件專案的通電日期、IT 負載與分期啟用節點，因此無法將核准總額直接換算為年度可用容量。地點：馬來西亞（以半島地區資料中心走廊為主，Johor 與吉隆坡周邊最受關注）。</t>
           </r>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>對精密電源與量測設備業者而言，重點不是單一數字，而是機房是否能順利交付、通電與驗證。若客戶承租與供電節點仍未落地，設備採購節奏會被延後，這些資訊仍需要與長約條款一併核對。</t>
+          <t>對精密電源與量測設備業者而言，這批核准案代表可追蹤的工程與接電需求管線，而不是立即可認列的設備銷售。下一步要核對的是分期上線節點、電網可用餘裕與實際租戶導入速度。</t>
         </is>
       </c>
     </row>

--- a/docs/exports/week-2026-10-18.xlsx
+++ b/docs/exports/week-2026-10-18.xlsx
@@ -143,7 +143,7 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF3B4A44"/>
             </rPr>
-            <t xml:space="preserve">台灣展會和NVIDIA、聯電及愛普公告揭露載板、晶片測試、CPO光學引擎與矽電容的新驗證或擴產節點；矽品規劃2027年中將光學引擎產能提升至現有15倍，愛普Gen2D已完成初步晶圓驗證。馬來西亞及泰國則有銅箔、CCL與焊球產能規劃，相關認證和實際產出仍待公開。</t>
+            <t xml:space="preserve">台灣展會和 NVIDIA、聯電及愛普公告揭露載板、晶片測試、CPO 光學引擎與矽電容的新驗證或擴產節點；矽品規劃 2027 年中將光學引擎產能提升至現有 15 倍，愛普 Gen2D 已完成初步晶圓驗證。馬來西亞及泰國則有銅箔、CCL 與焊球產能規劃，相關認證和實際產出仍待公開。</t>
           </r>
         </is>
       </c>
@@ -177,7 +177,7 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF3B4A44"/>
             </rPr>
-            <t xml:space="preserve">台灣9月外銷訂單達1,142.1億美元、馬來西亞同期出口年增54.5%，台綜院另報9月半導體用電年增11.55%。三組數據的地域、統計範圍與基期不同，半導體用電無法直接換算為晶圓出貨。</t>
+            <t xml:space="preserve">台灣 9 月外銷訂單達 1,142.1 億美元、馬來西亞同期出口年增 54.5%，台綜院另報 9 月半導體用電年增 11.55%。三組數據的地域、統計範圍與基期不同，半導體用電無法直接換算為晶圓出貨。</t>
           </r>
         </is>
       </c>
@@ -187,7 +187,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="82" customHeight="1">
+    <row r="5" ht="98" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">03</t>
@@ -202,16 +202,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">記憶體：美光勞資進度與馬日ZAM設計合作
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">美光台中工會10月21日達成協議，桃園工會22日有11名幹部展開行動；公司另公布季度分潤及台灣勞退提撥調升。馬來西亞SkyeChip與日本SAIMEMORY合作新型記憶體架構研發，尚未公布樣品良率或量產計畫。</t>
+            <t xml:space="preserve">記憶體：美光勞資進度與馬日 ZAM 設計合作
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">美光台中工會 10 月 21 日達成協議，桃園工會 22 日有 11 名幹部展開行動；公司另公布季度分潤及台灣勞退提撥調升。馬來西亞 SkyeChip 與日本 SAIMEMORY 合作新型記憶體架構研發，尚未公布樣品良率或量產計畫。</t>
           </r>
         </is>
       </c>
@@ -236,16 +236,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">AI資料中心系統：台灣ODM與模組化機房交付
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">神雲台灣擴廠、東南亞機房計畫與NVIDIA DSX POD新型模組化AI機房依不同進度推進，DSX POD列名鴻海、台達電、技嘉、和碩、雲達及緯創等合作廠商。最快14天部署是備妥案場條件的公司估算，與已上線機房容量不能混用。</t>
+            <t xml:space="preserve">AI 資料中心系統：台灣 ODM 與模組化機房交付
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">神雲台灣擴廠、東南亞機房計畫與 NVIDIA DSX POD 新型模組化 AI 機房依不同進度推進，DSX POD 列名鴻海、台達電、技嘉、和碩、雲達及緯創等合作廠商。最快 14 天部署是備妥案場條件的公司估算，與已上線機房容量不能混用。</t>
           </r>
         </is>
       </c>
@@ -255,7 +255,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="82" customHeight="1">
+    <row r="7" ht="98" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">05</t>
@@ -279,7 +279,7 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF3B4A44"/>
             </rPr>
-            <t xml:space="preserve">台積電高雄F22工地事故造成4名工人死亡並暫停同類作業；Reuters另報導台積電正洽詢設備馬達降低稀土使用量，尚未獲原廠證實。新加坡製造AI補助與馬來西亞半導體人才培訓資金均為計畫或核准支出，與實際產線投產不同。</t>
+            <t xml:space="preserve">台積電高雄 F22 工地事故造成 4 名工人死亡並暫停同類作業；Reuters 另報導台積電正洽詢設備馬達降低稀土使用量，尚未獲原廠證實。新加坡製造 AI 補助與馬來西亞半導體人才培訓資金均為計畫或核准支出，與實際產線投產不同。</t>
           </r>
         </is>
       </c>
@@ -668,7 +668,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="210" customHeight="1">
+    <row r="12" ht="246" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
@@ -683,16 +683,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">NVIDIA公布京元電11億美元預付款，矽品光學引擎規劃增產15倍
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">NVIDIA 10月21日在柏林GTC宣布，規劃以11億美元測試產能預訂預付款支持京元電美國新廠，目標2027年4月量產；矽品台灣CPO光學引擎產能目標2027年中提升至現有15倍。欣興台灣KF載板擴產預定2027年第2季起增加產能，均為未來計畫。公告跨越晶片載板、晶圓級封裝、測試與光學引擎。京元電提供晶片測試，矽品負責CPO光學引擎，欣興提供先進封裝載板；NVIDIA並預期2027年集團半導體測試產能較2026年翻倍，包含美國、台灣與新加坡擴充。NVIDIA表示新加坡測試產能計畫2027年2月開始大規模生產；矽品產能於2028年底前另力求再翻倍。與京元電的11億美元為產能預訂預付款，不能列為已完成廠房投資或公司營收。各項基準月產量、設備到廠、客戶驗收、實際預付款撥付與投產率未公布。地點：德國柏林 GTC 會議（發布活動）；台灣、美國與新加坡擴建廠址尚無完整地點明細。</t>
+            <t xml:space="preserve">NVIDIA 公布京元電 11 億美元預付款，矽品光學引擎規劃增產 15 倍
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">NVIDIA 10 月 21 日在柏林 GTC 宣布，規劃以 11 億美元測試產能預訂預付款支持京元電美國新廠，目標 2027 年 4 月量產；矽品台灣 CPO 光學引擎產能目標 2027 年中提升至現有 15 倍。欣興台灣 KF 載板擴產預定 2027 年第 2 季起增加產能，均為未來計畫。公告跨越晶片載板、晶圓級封裝、測試與光學引擎。京元電提供晶片測試，矽品負責 CPO 光學引擎，欣興提供先進封裝載板；NVIDIA 並預期 2027 年集團半導體測試產能較 2026 年翻倍，包含美國、台灣與新加坡擴充。NVIDIA 表示新加坡測試產能計畫 2027 年 2 月開始大規模生產；矽品產能於 2028 年底前另力求再翻倍。與京元電的 11 億美元為產能預訂預付款，不能列為已完成廠房投資或公司營收。各項基準月產量、設備到廠、客戶驗收、實際預付款撥付與投產率未公布。地點：德國柏林 GTC 會議（發布活動）；台灣、美國與新加坡擴建廠址尚無完整地點明細。</t>
           </r>
         </is>
       </c>
@@ -701,7 +701,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">對封測機台、測試量測、基板製程電源與光學模組供應商而言，可核對2027年京元電設備裝機、矽品CPO光學引擎合格產出及欣興KF載板認證節點。公告未提供基準產出和最終採購量，無法從倍率推算設備需求。</t>
+          <t xml:space="preserve">對封測機台、測試量測、基板製程電源與光學模組供應商而言，可核對 2027 年京元電設備裝機、矽品 CPO 光學引擎合格產出及欣興 KF 載板認證節點。公告未提供基準產出和最終採購量，無法從倍率推算設備需求。</t>
         </is>
       </c>
     </row>
@@ -720,16 +720,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">聯電與愛普合作矽電容，Gen2D已完成投片和初步驗證
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">聯電與愛普10月22日在新竹宣布深溝槽電容（DTC）晶圓製造與S-SiCap矽電容設計合作。愛普Gen2D產品已於第三季完成投片和初步功能驗證，後續將進行封裝基板系統級效能與可靠度測試；雙方尚未宣布客戶量產驗收。DTC矽電容可配置於晶片附近、中介層、封裝基板或封裝底部，降低供電路徑阻抗，與既有PCB上的穩壓元件形成不同整合層級。這項合作連結晶圓代工、先進封裝、電容元件與資料中心晶片供電完整性。聯電提供可擴充晶圓製程，愛普提供客製化矽電容與系統整合。公司表示也在探索內埋中介層電容及封裝底部電容產品線；相關新製造投資尚未公布金額。系統級測試結果、耐壓電容規格、量產良率、客戶導入時點與擴建金額未公布。</t>
+            <t xml:space="preserve">聯電與愛普合作矽電容，Gen2D 已完成投片和初步驗證
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">聯電與愛普 10 月 22 日在新竹宣布深溝槽電容（DTC）晶圓製造與 S-SiCap 矽電容設計合作。愛普 Gen2D 產品已於第三季完成投片和初步功能驗證，後續將進行封裝基板系統級效能與可靠度測試；雙方尚未宣布客戶量產驗收。DTC 矽電容可配置於晶片附近、中介層、封裝基板或封裝底部，降低供電路徑阻抗，與既有 PCB 上的穩壓元件形成不同整合層級。這項合作連結晶圓代工、先進封裝、電容元件與資料中心晶片供電完整性。聯電提供可擴充晶圓製程，愛普提供客製化矽電容與系統整合。公司表示也在探索內埋中介層電容及封裝底部電容產品線；相關新製造投資尚未公布金額。系統級測試結果、耐壓電容規格、量產良率、客戶導入時點與擴建金額未公布。</t>
           </r>
         </is>
       </c>
@@ -738,7 +738,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">對電源轉換、晶圓製程與封裝量測業者，值得核對DTC的電壓規格、可靠度測試方法、封裝整合良率和客戶設計導入狀況。目前沒有量產承諾或交貨量可判斷後續需求。</t>
+          <t xml:space="preserve">對電源轉換、晶圓製程與封裝量測業者，值得核對 DTC 的電壓規格、可靠度測試方法、封裝整合良率和客戶設計導入狀況。目前沒有量產承諾或交貨量可判斷後續需求。</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="162" customHeight="1">
+    <row r="17" ht="178" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
@@ -868,16 +868,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">台綜院：9月半導體用電首破45億度，年增11.55%
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台灣綜合研究院10月21日公布，2026年9月台灣半導體業用電量首次突破45億度，較去年同期增加11.55%；製造業高壓以上用電年增1.96%。台綜院預估全年半導體用電超過500億度，屬研究機構估計，並非全年已發生實績。半導體用電涵蓋晶圓、封裝與公用廠務負載，可作為生產活動的間接參考，但用電升高亦可能來自新廠試產、設備配置與能效因素，不能直接換算晶圓出貨。台綜院同時公布9月全國高壓以上產業用電年增1.76%，半導體分項年增11.55%；其2026全年500億度估計尚待後續實際統計驗證。未取得研究院原始月報表，各產業用電分項基期度數、個別廠區負載及全年實際用量無法核對。</t>
+            <t xml:space="preserve">台綜院：9 月半導體用電首破 45 億度，年增 11.55%
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台灣綜合研究院 10 月 21 日公布，2026 年 9 月台灣半導體業用電量首次突破 45 億度，較去年同期增加 11.55%；製造業高壓以上用電年增 1.96%。台綜院預估全年半導體用電超過 500 億度，屬研究機構估計，並非全年已發生實績。半導體用電涵蓋晶圓、封裝與公用廠務負載，可作為生產活動的間接參考，但用電升高亦可能來自新廠試產、設備配置與能效因素，不能直接換算晶圓出貨。台綜院同時公布 9 月全國高壓以上產業用電年增 1.76%，半導體分項年增 11.55%；其 2026 全年 500 億度估計尚待後續實際統計驗證。未取得研究院原始月報表，各產業用電分項基期度數、個別廠區負載及全年實際用量無法核對。</t>
           </r>
         </is>
       </c>
@@ -964,7 +964,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="178" customHeight="1">
+    <row r="20" ht="194" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
@@ -979,16 +979,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">追蹤：美光桃園11名工會幹部罷工，公布季度分潤及勞退調升
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">美光桃園工會11名幹部10月22日上午9時起展開24小時罷工，台中工會則已於前一天達成協議。美光同日公布季度分潤獎金採現金與股票各半，台灣員工勞退提撥率由8%提高至10%，並增3天有薪假；實際產線損失仍未披露。桃園廠牽涉DRAM前段晶圓製造，台中廠有先進DRAM、HBM與封裝測試。工會幹部參與行動的實際規模，不能直接推算成整座晶圓廠停產時間。美光管理階層表示本次協議新增季度分潤，現金部分於每季財報後發放，股票獎勵一年後歸屬。公司亦公布輪班津貼和結構性調薪調整，桃園工會仍要求持續對話。未公布工廠產能利用率、實際出貨損失、桃園工會是否接受新方案及台中協議條款全文。地點：台灣桃園美光工廠外（實際工會行動地點，依中央社報導）。</t>
+            <t xml:space="preserve">追蹤：美光桃園 11 名工會幹部罷工，公布季度分潤及勞退調升
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">美光桃園工會 11 名幹部 10 月 22 日上午 9 時起展開 24 小時罷工，台中工會則已於前一天達成協議。美光同日公布季度分潤獎金採現金與股票各半，台灣員工勞退提撥率由 8% 提高至 10%，並增 3 天有薪假；實際產線損失仍未披露。桃園廠牽涉 DRAM 前段晶圓製造，台中廠有先進 DRAM、HBM 與封裝測試。工會幹部參與行動的實際規模，不能直接推算成整座晶圓廠停產時間。美光管理階層表示本次協議新增季度分潤，現金部分於每季財報後發放，股票獎勵一年後歸屬。公司亦公布輪班津貼和結構性調薪調整，桃園工會仍要求持續對話。未公布工廠產能利用率、實際出貨損失、桃園工會是否接受新方案及台中協議條款全文。地點：台灣桃園美光工廠外（實際工會行動地點，依中央社報導）。</t>
           </r>
         </is>
       </c>
@@ -997,11 +997,11 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">製程電源與記憶體測試供應商可核實罷工當日的輪班覆蓋、設備維護及在製品狀態，並留意薪酬協商對工廠排程是否有具體變動。現階段11名工會幹部的行動不足以估算設備需求或良率影響。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="198" customHeight="1">
+          <t xml:space="preserve">製程電源與記憶體測試供應商可核實罷工當日的輪班覆蓋、設備維護及在製品狀態，並留意薪酬協商對工廠排程是否有具體變動。現階段 11 名工會幹部的行動不足以估算設備需求或良率影響。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="214" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
@@ -1016,16 +1016,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">馬來西亞SkyeChip與日本SAIMEMORY合作ZAM新型AI記憶體設計
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">日本SAIMEMORY與馬來西亞SkyeChip於10月21日宣布設計工程合作，由SkyeChip提供記憶體介面、矽晶片設計及客製化IP，參與面向AI資料中心的Z-Angle Memory（ZAM）開發。官方公告未提供原型測試結果、記憶體頻寬或量產時程。SAIMEMORY為SoftBank旗下技術公司，ZAM定位為高容量、高頻寬及降低功耗的記憶體架構；SkyeChip提供IP設計、驗證與整合能力。這是新型記憶體研發合作，尚未等同HBM產線建成。合作在日本NEDO補助的Post-5G基礎設施研發計畫下進行。官方公告著重工程支援與未來商業化意向，未披露交付規格和產線資本支出。ZAM原型良率、傳輸頻寬、功耗測試、客戶樣品及商業量產日期尚未公布。</t>
+            <t xml:space="preserve">馬來西亞 SkyeChip 與日本 SAIMEMORY 合作 ZAM 新型 AI 記憶體設計
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">日本 SAIMEMORY 與馬來西亞 SkyeChip 於 10 月 21 日宣布設計工程合作，由 SkyeChip 提供記憶體介面、矽晶片設計及客製化 IP，參與面向 AI 資料中心的 Z-Angle Memory（ZAM）開發。官方公告未提供原型測試結果、記憶體頻寬或量產時程。SAIMEMORY 為 SoftBank 旗下技術公司，ZAM 定位為高容量、高頻寬及降低功耗的記憶體架構；SkyeChip 提供 IP 設計、驗證與整合能力。這是新型記憶體研發合作，尚未等同 HBM 產線建成。合作在日本 NEDO 補助的 Post-5G 基礎設施研發計畫下進行。官方公告著重工程支援與未來商業化意向，未披露交付規格和產線資本支出。ZAM 原型良率、傳輸頻寬、功耗測試、客戶樣品及商業量產日期尚未公布。</t>
           </r>
         </is>
       </c>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">記憶體電源、測試及高速介面供應商應查詢ZAM的實際電壓、頻寬、封裝介面與驗證方法。現階段缺少樣品量產、封裝基板及測試產能資訊。</t>
+          <t xml:space="preserve">記憶體電源、測試及高速介面供應商應查詢 ZAM 的實際電壓、頻寬、封裝介面與驗證方法。現階段缺少樣品量產、封裝基板及測試產能資訊。</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF3B4A44"/>
             </rPr>
-            <t xml:space="preserve">Bitdeer 於台灣時間 10 月 20 日公布 9 月未經審計營運更新，集團 AI Cloud GPU 利用率由 8 月 92% 升至 95%，已部署 GPU 維持 4,328 顆。馬來西亞柔佛新山 A201 約 21.7 MW 計畫已有逾七成長約涵蓋，仍未全面上線，機房就緒與完整部署列為不同節點。GPU 訂閱服務連結伺服器機櫃、電源轉換、液冷與機房供電。9 月外部訂閱 GPU 為 4,007 顆，8 月為 3,998 顆；這些是集團合計，不是馬來西亞單一基地數字。公司另列馬來西亞 A101 的 2.5 MW 已上線，與 A201 規劃容量分開。公司列 9 月年化收入運行率約 8,600 萬美元、收入儲備約 29 億美元，8 月分別為 8,600 萬及 9 億美元。前者按月底當日契約 GPU 收入乘 365，後者為未來合約收入，不是已認列年度營收。A201 表格列 2027 年 1 月機房就緒，正文列同年 4 月完整部署及上線目標，並稱已採購逾 100 櫃 GB300 NVL72。數字為公司未經審計更新；A201 一月機房就緒與四月全面上線的驗收定義、實際通電及收入認列時點未完整說明。地點：專案地點：馬來西亞柔佛州新山 A201 資料中心；公告另列馬來西亞 A101 已上線。</t>
+            <t xml:space="preserve">Bitdeer 於台灣時間 10 月 20 日公布 9 月未經審計營運更新，集團 AI Cloud GPU 利用率由 8 月 92% 升至 95%，已部署 GPU 維持 4,328 顆。馬來西亞柔佛新山 A201 約 21.7MW 計畫已有逾七成長約涵蓋，仍未全面上線，機房就緒與完整部署列為不同節點。GPU 訂閱服務連結伺服器機櫃、電源轉換、液冷與機房供電。9 月外部訂閱 GPU 為 4,007 顆，8 月為 3,998 顆；這些是集團合計，不是馬來西亞單一基地數字。公司另列馬來西亞 A101 的 2.5MW 已上線，與 A201 規劃容量分開。公司列 9 月年化收入運行率約 8,600 萬美元、收入儲備約 29 億美元，8 月分別為 8,600 萬及 9 億美元。前者按月底當日契約 GPU 收入乘 365，後者為未來合約收入，不是已認列年度營收。A201 表格列 2027 年 1 月機房就緒，正文列同年 4 月完整部署及上線目標，並稱已採購逾 100 櫃 GB300 NVL72。數字為公司未經審計更新；A201 一月機房就緒與四月全面上線的驗收定義、實際通電及收入認列時點未完整說明。地點：專案地點：馬來西亞柔佛州新山 A201 資料中心；公告另列馬來西亞 A101 已上線。</t>
           </r>
         </is>
       </c>
@@ -1127,16 +1127,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">Aolani 簽馬來西亞最高 500 MW 意向書，仍待正式協議
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">新加坡 Aolani 10 月 19 日宣布，已簽意向書擬取得馬來西亞多處最高 500 MW AI 資料中心容量，目標自 2027 年下半年開始上線。公司明列意向書不具約束力，須再洽簽正式協議，未公開基地城市、供電條件或投資金額。Aolani 將提供 AI 基礎設施、GPU 部署及營運需求；機房屬設計符合 Tier III，未稱已獲認證。公司稱 2026 年已承諾容量約 80 MW，目標 2027 年合計最高 580 MW；80 MW 不是已營運容量、580 MW 也不是此次新增量。官網與 TNGlobal 日期為 10/19，ACCESS 發稿頁列 10/18 23:45、未註明時區，實際簽字日未列。意向書不具約束力；交易對手、基地、正式合約、供電核定、實際營運容量及簽署日期未公布。地點：專案地點：馬來西亞多處基地，城市及場址未公布；公告發布於新加坡。</t>
+            <t xml:space="preserve">Aolani 簽馬來西亞最高 500MW 意向書，仍待正式協議
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">新加坡 Aolani 10 月 19 日宣布，已簽意向書擬取得馬來西亞多處最高 500MW AI 資料中心容量，目標自 2027 年下半年開始上線。公司明列意向書不具約束力，須再洽簽正式協議，未公開基地城市、供電條件或投資金額。Aolani 將提供 AI 基礎設施、GPU 部署及營運需求；機房屬設計符合 Tier III，未稱已獲認證。公司稱 2026 年已承諾容量約 80MW，目標 2027 年合計最高 580MW；80MW 不是已營運容量、580MW 也不是此次新增量。官網與 TNGlobal 日期為 10/19，ACCESS 發稿頁列 10/18 23:45、未註明時區，實際簽字日未列。意向書不具約束力；交易對手、基地、正式合約、供電核定、實際營運容量及簽署日期未公布。地點：專案地點：馬來西亞多處基地，城市及場址未公布；公告發布於新加坡。</t>
           </r>
         </is>
       </c>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">對資料中心電源轉換、配電量測及散熱控制業者而言，須先辨識意向容量對應的場址、業主與 GPU 營運分工。正式供電核定、機櫃規格及驗收時程均未公開，無法由 500 MW 意向推定已成立的設備需求。</t>
+          <t xml:space="preserve">對資料中心電源轉換、配電量測及散熱控制業者而言，須先辨識意向容量對應的場址、業主與 GPU 營運分工。正式供電核定、機櫃規格及驗收時程均未公開，無法由 500MW 意向推定已成立的設備需求。</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="214" customHeight="1">
+    <row r="26" ht="230" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">24</t>
@@ -1201,16 +1201,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">NVIDIA推出DSX POD模組化AI機房，鴻海與台灣ODM列合作供應商
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">NVIDIA 10月21日在德國柏林公布以Vera Rubin為核心的DSX POD模組化AI工廠參考設計，合作廠商包括鴻海鴻佰、台達電、技嘉、和碩、雲達及緯創。NVIDIA稱已備妥現場基礎設施的案場部署可由6個月縮短至最快14天，全球合作交付目標為2027年初。DSX POD將伺服器整機、配線、機櫃電源、網路與液冷管路的整合測試提前在工廠完成；交付後仍須案場電力、散熱與網路就緒。台灣合作廠商分布在ODM、電源與機櫃系統。所稱14天為NVIDIA參考設計在已備妥案場條件下的最快目標，6個月為其比較情境，非所有專案實績。公司未列個別台廠供貨量與認證時程。個別客戶訂單、機櫃實際額定電力、液冷驗收、部署現場、交付數量均未公布。地點：德國柏林 GTC 開發者大會（發布會場）；模組化機房實際專案場址尚未公布。</t>
+            <t xml:space="preserve">NVIDIA 推出 DSX POD 模組化 AI 機房，鴻海與台灣 ODM 列合作供應商
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">NVIDIA 10 月 21 日在德國柏林公布以 Vera Rubin 為核心的 DSX POD 模組化 AI 工廠參考設計，合作廠商包括鴻海鴻佰、台達電、技嘉、和碩、雲達及緯創。NVIDIA 稱已備妥現場基礎設施的案場部署可由 6 個月縮短至最快 14 天，全球合作交付目標為 2027 年初。DSX POD 將伺服器整機、配線、機櫃電源、網路與液冷管路的整合測試提前在工廠完成；交付後仍須案場電力、散熱與網路就緒。台灣合作廠商分布在 ODM、電源與機櫃系統。所稱 14 天為 NVIDIA 參考設計在已備妥案場條件下的最快目標，6 個月為其比較情境，非所有專案實績。公司未列個別台廠供貨量與認證時程。個別客戶訂單、機櫃實際額定電力、液冷驗收、部署現場、交付數量均未公布。地點：德國柏林 GTC 開發者大會（發布會場）；模組化機房實際專案場址尚未公布。</t>
           </r>
         </is>
       </c>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">資料中心電源轉換、液冷CDU、機櫃測試業者可核實箱體出廠的功能驗證範圍、現場變電與散熱介面，以及各ODM責任分工。最短部署時間仍是估計，尚無可比較的實際交付數據。</t>
+          <t xml:space="preserve">資料中心電源轉換、液冷 CDU、機櫃測試業者可核實箱體出廠的功能驗證範圍、現場變電與散熱介面，以及各 ODM 責任分工。最短部署時間仍是估計，尚無可比較的實際交付數據。</t>
         </is>
       </c>
     </row>
@@ -1238,16 +1238,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">鴻海等業者簽表後儲能協議，規劃 306 kWh 電池櫃與 2027 年供貨
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">鴻海與台灣儲能團隊 10 月 16 日在 Energy Taiwan 展期宣布簽署合作協議，規劃單櫃 306 kWh 的國產化表後儲能電池系統。團隊目標於 2027 年上半年完成認證及正式供貨，2027 年累計建置 100 MWh；兩項時間與規模均為目標。鴻海提供國產電芯，合作團隊包含利佳興業、盛達旗下盛齊綠能與晟瑞科技等業者，整合代工、工程與客戶服務。公司表示可供應單一電池直流櫃，或整合電力轉換系統 PCS 與能源管理系統 EMS，對應工商業儲能及需量管理。306 kWh 為單櫃規劃能量，100 MWh 為 2027 年累計市場建置目標，範圍與期間均不同。團隊預計 2026 年完成直流櫃開發，再於 2027 上半年完成認證與供貨，未提供可比較的既有安裝基數。尚未公布完成認證、正式供貨或已驗收建置實績；306 kWh 是儲存能量，公告未列 PCS 額定輸出功率，不能換作 306 kW。地點：展會場地：台灣台北南港展覽館一館；Energy Taiwan 展期為 10/14 至 10/16。新聞稿未另列簽約儀式室別。</t>
+            <t xml:space="preserve">鴻海等業者簽表後儲能協議，規劃 306kWh 電池櫃與 2027 年供貨
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">鴻海與台灣儲能團隊 10 月 16 日在 Energy Taiwan 展期宣布簽署合作協議，規劃單櫃 306kWh 的國產化表後儲能電池系統。團隊目標於 2027 年上半年完成認證及正式供貨，2027 年累計建置 100 MWh；兩項時間與規模均為目標。鴻海提供國產電芯，合作團隊包含利佳興業、盛達旗下盛齊綠能與晟瑞科技等業者，整合代工、工程與客戶服務。公司表示可供應單一電池直流櫃，或整合電力轉換系統 PCS 與能源管理系統 EMS，對應工商業儲能及需量管理。306kWh 為單櫃規劃能量，100 MWh 為 2027 年累計市場建置目標，範圍與期間均不同。團隊預計 2026 年完成直流櫃開發，再於 2027 上半年完成認證與供貨，未提供可比較的既有安裝基數。尚未公布完成認證、正式供貨或已驗收建置實績；306kWh 是儲存能量，公告未列 PCS 額定輸出功率，不能換作 306kW。地點：展會場地：台灣台北南港展覽館一館；Energy Taiwan 展期為 10/14 至 10/16。新聞稿未另列簽約儀式室別。</t>
           </r>
         </is>
       </c>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">對電力轉換與量測控制供應商而言，相關客戶包括電池系統整合商與工商用戶，介面涉及 PCS、EMS 及現場驗收。值得核對額定功率、通訊規格與認證要求；306 kWh 與 100 MWh 分別是規格及目標，不能據以推算已下單的轉換器數量。</t>
+          <t xml:space="preserve">對電力轉換與量測控制供應商而言，相關客戶包括電池系統整合商與工商用戶，介面涉及 PCS、EMS 及現場驗收。值得核對額定功率、通訊規格與認證要求；306kWh 與 100 MWh 分別是規格及目標，不能據以推算已下單的轉換器數量。</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF3B4A44"/>
             </rPr>
-            <t xml:space="preserve">Reuters 10月22日引述3名知情人士指出，台積電正調查半導體自動化設備使用低稀土或無稀土馬達的可能性，以降低部分設備供應受出口管制影響。報導指出供應商洽詢尚處早期，未有廣泛導入；台積電拒絕評論。稀土永磁材料可用於精密定位與自動化設備馬達，連結晶圓廠產線零組件與設備維護。報導所述風險來源為中國既有稀土及磁材出口管制，尚無特定台積電產線因短缺停工的證據。Reuters另引述工研院聲明，台灣正與經濟部產業技術司規劃稀土相關技術專案。工研院過去提及試量產線及供應目標屬先前政策背景，不能視為10月22日新增產能。未取得台積電直接公告，無供應商、馬達規格、設備替換數量或導入時間表；屬報導引述的評估。</t>
+            <t xml:space="preserve">Reuters 10 月 22 日引述 3 名知情人士指出，台積電正調查半導體自動化設備使用低稀土或無稀土馬達的可能性，以降低部分設備供應受出口管制影響。報導指出供應商洽詢尚處早期，未有廣泛導入；台積電拒絕評論。稀土永磁材料可用於精密定位與自動化設備馬達，連結晶圓廠產線零組件與設備維護。報導所述風險來源為中國既有稀土及磁材出口管制，尚無特定台積電產線因短缺停工的證據。Reuters 另引述工研院聲明，台灣正與經濟部產業技術司規劃稀土相關技術專案。工研院過去提及試量產線及供應目標屬先前政策背景，不能視為 10 月 22 日新增產能。未取得台積電直接公告，無供應商、馬達規格、設備替換數量或導入時間表；屬報導引述的評估。</t>
           </r>
         </is>
       </c>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="178" customHeight="1">
+    <row r="35" ht="194" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">33</t>
@@ -1534,16 +1534,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">馬國國會披露半導體培訓核准4,767萬令吉，涵蓋1.9萬名額
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">馬來西亞貿工部長10月22日經媒體報導向國會指出，HRD Corp已於8月核准4,767萬令吉高科技培訓補助，涵蓋19,084個名額及9類半導體相關技能。截至2026年第3季，累計已有22,849名勞工完成各項相關訓練；這些數字各屬不同統計期間，不能直接相減作為未完成名額。培訓項目涵蓋IC設計、先進封裝、自動化及數位技術，是國家半導體策略人力供給的一環。2030年6萬名高技能工程師是政策目標，不能視為已受訓人數。依The Star引述，款項是在2026年8月獲核准；10月22日的新資訊為國會披露最新累計訓練進度。官方國會紀錄及核准項目細表未取得。未取得國會逐字稿、各訓練方案完訓率、實際支出及人才投入半導體公司的比例。</t>
+            <t xml:space="preserve">馬國國會披露半導體培訓核准 4,767 萬令吉，涵蓋 1.9 萬名額
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">馬來西亞貿工部長 10 月 22 日經媒體報導向國會指出，HRD Corp 已於 8 月核准 4,767 萬令吉高科技培訓補助，涵蓋 19,084 個名額及 9 類半導體相關技能。截至 2026 年第 3 季，累計已有 22,849 名勞工完成各項相關訓練；這些數字各屬不同統計期間，不能直接相減作為未完成名額。培訓項目涵蓋 IC 設計、先進封裝、自動化及數位技術，是國家半導體策略人力供給的一環。2030 年 6 萬名高技能工程師是政策目標，不能視為已受訓人數。依 The Star 引述，款項是在 2026 年 8 月獲核准；10 月 22 日的新資訊為國會披露最新累計訓練進度。官方國會紀錄及核准項目細表未取得。未取得國會逐字稿、各訓練方案完訓率、實際支出及人才投入半導體公司的比例。</t>
           </r>
         </is>
       </c>

--- a/docs/exports/week-2026-10-18.xlsx
+++ b/docs/exports/week-2026-10-18.xlsx
@@ -134,16 +134,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">先進封裝與高速互連：載板、光學引擎、矽電容及材料
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台灣展會和 NVIDIA、聯電及愛普公告揭露載板、晶片測試、CPO 光學引擎與矽電容的新驗證或擴產節點；矽品規劃 2027 年中將光學引擎產能提升至現有 15 倍，愛普 Gen2D 已完成初步晶圓驗證。馬來西亞及泰國則有銅箔、CCL 與焊球產能規劃，相關認證和實際產出仍待公開。</t>
+            <t xml:space="preserve">先進封裝、測試與高速互連：設備與材料擴建
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">本週公告涵蓋台灣載板、矽電容、光學引擎、測試設備及封裝材料，漢測 10 月 22 日新增 64 億元的研發與探針卡設備製造預算授權。新台幣預算屬董事會核准額，京元電產能預付款及矽品倍數則屬不同計畫，認證和實際出貨尚需分開查證。</t>
           </r>
         </is>
       </c>
@@ -153,7 +153,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="82" customHeight="1">
+    <row r="4" ht="98" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">02</t>
@@ -168,22 +168,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">晶圓製造與電子需求：訂單、出口和電力負載
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台灣 9 月外銷訂單達 1,142.1 億美元、馬來西亞同期出口年增 54.5%，台綜院另報 9 月半導體用電年增 11.55%。三組數據的地域、統計範圍與基期不同，半導體用電無法直接換算為晶圓出貨。</t>
+            <t xml:space="preserve">晶圓製造與電子需求：外銷訂單、出口及 9 月生產
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台灣 9 月外銷訂單達 1,142.1 億美元，10 月 23 日公布的製造業生產指數年增 20.21%，積體電路業年增 26.51%；馬來西亞 9 月出口亦年增 54.5%。製造業指數低於原預估區間，且外銷訂單、實際生產及用電數字不能直接合計。</t>
           </r>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/16、10/19、10/20、10/21</t>
+          <t xml:space="preserve">10/16、10/19、10/20、10/21、10/23</t>
         </is>
       </c>
     </row>
@@ -202,22 +202,22 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">記憶體：美光勞資進度與馬日 ZAM 設計合作
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">美光台中工會 10 月 21 日達成協議，桃園工會 22 日有 11 名幹部展開行動；公司另公布季度分潤及台灣勞退提撥調升。馬來西亞 SkyeChip 與日本 SAIMEMORY 合作新型記憶體架構研發，尚未公布樣品良率或量產計畫。</t>
+            <t xml:space="preserve">記憶體供應：美光桃園協商進度及馬日設計合作
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">美光台中工會 21 日達成協議，桃園工會幹部 22 日罷工，23 日公布 1,633 名會員反對公司方案，協商延至 27 日。另一方面，馬來西亞 SkyeChip 與日本 SAIMEMORY 公布新型記憶體設計合作，尚無產品量產資料。</t>
           </r>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/20、10/21、10/22</t>
+          <t xml:space="preserve">10/20、10/21、10/22、10/23</t>
         </is>
       </c>
     </row>
@@ -236,26 +236,26 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">AI 資料中心系統：台灣 ODM 與模組化機房交付
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">神雲台灣擴廠、東南亞機房計畫與 NVIDIA DSX POD 新型模組化 AI 機房依不同進度推進，DSX POD 列名鴻海、台達電、技嘉、和碩、雲達及緯創等合作廠商。最快 14 天部署是備妥案場條件的公司估算，與已上線機房容量不能混用。</t>
+            <t xml:space="preserve">資料中心與晶片系統：台灣 ODM、CPU 合作及新加坡展會
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">本週涵蓋神雲擴廠、資料中心機房計畫、NVIDIA 模組化機房設計、神盾與法國 SiPearl 的 CPU 晶片合作，以及台灣預定 33 家新創赴新加坡展覽。系統開發合作、設備交付目標及預定投資交流未揭露相同口徑的已交付營運容量。</t>
           </r>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/19、10/21</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="98" customHeight="1">
+          <t xml:space="preserve">10/19、10/21、10/22、10/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="82" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">05</t>
@@ -270,16 +270,16 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
-            <t xml:space="preserve">擴廠執行條件：施工、設備材料、人才與電力
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">台積電高雄 F22 工地事故造成 4 名工人死亡並暫停同類作業；Reuters 另報導台積電正洽詢設備馬達降低稀土使用量，尚未獲原廠證實。新加坡製造 AI 補助與馬來西亞半導體人才培訓資金均為計畫或核准支出，與實際產線投產不同。</t>
+            <t xml:space="preserve">工廠擴張條件：工安、電力、設備材料與出口管制
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">台積電高雄工地事故後同類鋼構作業暫停，另有設備稀土替代評估；漢翔 22 日啟用 9MW／54MWh 工業微電網，貿易署同日新增 343 個受管制實體。工廠設備、廠務供電與出口管制各有不同的技術、施工及法定查核條件。</t>
           </r>
         </is>
       </c>
@@ -742,7 +742,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="230" customHeight="1">
+    <row r="14" ht="194" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
@@ -757,6 +757,43 @@
               <rFont val="PingFang TC"/>
               <color rgb="FF14322B"/>
             </rPr>
+            <t xml:space="preserve">漢測董事會授權 64 億元，規劃研發中心與探針卡設備製造產線
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">漢民測試系統 10 月 22 日公告，董事會核准新竹研發中心與中南部製造中心兩項預算授權，合計新台幣 64 億元。製造中心規劃矽光子設備組裝、MEMS 及薄膜探針卡、回焊設備與雷射清針機產線，實際支出會依市場及工程進度調整。MEMS 探針卡是晶圓測試與封裝前電性驗證的重要耗材和設備介面；矽光子設備涉及光學封裝組裝及量測。公司目前公布的是授權預算，不能直接視為設備完成採購或產線已投產。新竹研發中心房屋與裝修投資上限 15 億元，中南部製造中心廠房 37 億元、設備 12 億元，合計 64 億元；董事長可在總預算 10% 範圍內依實際需求調整。中南部中心的確切城市、土地位置、興建開工與設備驗收日期均未揭露。地點：台灣新竹（研發中心計畫）、台灣中南部（製造中心候選區域）；確切工地地址未公布。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="6">
+        <v>46317</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半導體測試電源、精密量測和探針卡製造設備業者可確認中南部廠的測試規格、產線類別、設備驗收節點與實際資本支出。授權總額尚未對應確定設備採購單。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="230" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
             <t xml:space="preserve">新加坡 9 月非石油本地出口年增 68.4%，對台出口年增 96.9%
 </t>
           </r>
@@ -770,22 +807,22 @@
           </r>
         </is>
       </c>
-      <c r="C14" s="6">
+      <c r="C15" s="6">
         <v>46311</v>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對精密電源與量測控制供應商而言，對台專用機械及 IC 出口提供跨境設備與製造活動的總體線索。值得核對的是機械子分類、價格與實體出貨量，以及客戶驗收時點；名目出口增幅與船體低基期不能直接轉成設備訂單判斷。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="226" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="16" ht="226" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -807,22 +844,22 @@
           </r>
         </is>
       </c>
-      <c r="C15" s="6">
+      <c r="C16" s="6">
         <v>46315</v>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">精密電源與量測設備業者可將資訊通信、電子產品與光學設備訂單分開查核，追問相關需求對應的終端品項與產線。統計尚無公司別、製造地及採購節點資料，無法推論特定設備訂單。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="230" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+    <row r="17" ht="230" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -844,22 +881,22 @@
           </r>
         </is>
       </c>
-      <c r="C16" s="6">
+      <c r="C17" s="6">
         <v>46314</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">精密電源、測試與工業量測業者會區分國內出口與再出口，並進一步查核設備、封測零組件及終端產品的稅則細目。總額仍不足以判斷個別封測廠設備稼動率或客戶採購。</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="178" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18" ht="178" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -881,22 +918,59 @@
           </r>
         </is>
       </c>
-      <c r="C17" s="6">
+      <c r="C18" s="6">
         <v>46316</v>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">半導體製程電源、廠務配電與量測業者可查明新增用電究竟來自既有廠稼動率或新產線啟動，以及功率品質與負載變化。單一月份用電成長不足以推論設備交期或需求。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="210" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+    <row r="19" ht="230" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">9 月製造業生產年增 20.21%，伺服器產品組合變動使月產出低於預期
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">經濟部 10 月 23 日公布台灣 9 月製造業生產指數 143.31，年增 20.21%，工業生產指數 140.76，年增 19.17%；積體電路業年增 26.51%，電腦電子產品及光學製品業年增 45.92%。製造業指數低於原先預估的 146.03 至 150.03，經濟部指出伺服器產品組合變動影響月產出。半導體晶圓代工、DRAM、IC 封測及載板生產同屬電子零組件供應鏈，9 月電子零組件業年增 23.62%。機械設備業另年增 26.02%，經濟部指出半導體廠先進製程與封測設備擴充為相關因素。經濟部表示 9 月電腦電子產品及光學製品業月減 15.38%，製造業實績低於先前預測；整體年增和個別產品月減屬不同比較期間。10 月製造業指數 141.56 至 145.86 為官方預測，非實績。9 月各類產品的實際出貨片數、訂單組成及伺服器型號比重未公布；經濟部原始附表未直接取得。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C19" s="6">
+        <v>46318</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">精密製程電源、封測量測與伺服器電力業者可釐清哪些成長來自實際設備稼動及產品組合變化，並核對伺服器品項調整對產線負載的影響。總體指數不含個別廠商訂單或設備採購資訊。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="210" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -918,22 +992,22 @@
           </r>
         </is>
       </c>
-      <c r="C18" s="6">
+      <c r="C20" s="6">
         <v>46315</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">測試、量測與製程電源業者會先釐清桃園與台中各廠作業狀態，以及是否涉及既有設備維護和新品驗證。罷工尚未發生，亦無經核實的產量損失數據，不能據此推論記憶體採購變化。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="242" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="21" ht="242" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -952,80 +1026,6 @@
               <color rgb="FF3B4A44"/>
             </rPr>
             <t xml:space="preserve">Reuters 10 月 21 日報導，美光與台中工會已簽署協議並撤回原訂 10 月 22 日的調解，條款未公開；桃園工會則表示談判未取得具體分紅數字，仍規劃自 22 日上午 9 時起在桃園廠外進行 24 小時罷工。桃園廠以 DRAM 前段晶圓製造為主，台中廠涵蓋先進 DRAM、HBM 及封裝測試，但罷工參與範圍、維持運轉的人力與實際產量影響尚未確認。TrendForce 分析師向 Reuters 表示，桃園主要進行 DRAM 前段晶圓製造，台中則生產先進 DRAM 與 HBM 並處理封裝測試。罷工是否轉化為供給變動，取決於實際參與的產線與人員，以及維護、製程監控與異常處理是否維持。台中工會協議與桃園工會罷工屬兩個不同勞資進程。美光表示仍希望持續對話；Reuters 報導時，桃園行動尚未開始，不能把預定 24 小時直接視為停產 24 小時。台中協議條款、桃園工會實際參與人數、受影響產線、在製品處置、良率及出貨排程均未公開。地點：台灣桃園，美光桃園廠外（工會預定罷工地點，依 Reuters 轉述）。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C19" s="6">
-        <v>46316</v>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">對半導體製程電源、量測與測試設備供應商而言，值得追問的是桃園廠實際維持運轉的人力、受影響機台與在製品節點，以及台中協議是否涵蓋關鍵技術人員。現有資料不足以判定 DRAM、HBM 或封裝測試設備的拉貨與維護節奏會改變。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="194" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">追蹤：美光桃園 11 名工會幹部罷工，公布季度分潤及勞退調升
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">美光桃園工會 11 名幹部 10 月 22 日上午 9 時起展開 24 小時罷工，台中工會則已於前一天達成協議。美光同日公布季度分潤獎金採現金與股票各半，台灣員工勞退提撥率由 8% 提高至 10%，並增 3 天有薪假；實際產線損失仍未披露。桃園廠牽涉 DRAM 前段晶圓製造，台中廠有先進 DRAM、HBM 與封裝測試。工會幹部參與行動的實際規模，不能直接推算成整座晶圓廠停產時間。美光管理階層表示本次協議新增季度分潤，現金部分於每季財報後發放，股票獎勵一年後歸屬。公司亦公布輪班津貼和結構性調薪調整，桃園工會仍要求持續對話。未公布工廠產能利用率、實際出貨損失、桃園工會是否接受新方案及台中協議條款全文。地點：台灣桃園美光工廠外（實際工會行動地點，依中央社報導）。</t>
-          </r>
-        </is>
-      </c>
-      <c r="C20" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">製程電源與記憶體測試供應商可核實罷工當日的輪班覆蓋、設備維護及在製品狀態，並留意薪酬協商對工廠排程是否有具體變動。現階段 11 名工會幹部的行動不足以估算設備需求或良率影響。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="214" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="13"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF14322B"/>
-            </rPr>
-            <t xml:space="preserve">馬來西亞 SkyeChip 與日本 SAIMEMORY 合作 ZAM 新型 AI 記憶體設計
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="11"/>
-              <rFont val="PingFang TC"/>
-              <color rgb="FF3B4A44"/>
-            </rPr>
-            <t xml:space="preserve">日本 SAIMEMORY 與馬來西亞 SkyeChip 於 10 月 21 日宣布設計工程合作，由 SkyeChip 提供記憶體介面、矽晶片設計及客製化 IP，參與面向 AI 資料中心的 Z-Angle Memory（ZAM）開發。官方公告未提供原型測試結果、記憶體頻寬或量產時程。SAIMEMORY 為 SoftBank 旗下技術公司，ZAM 定位為高容量、高頻寬及降低功耗的記憶體架構；SkyeChip 提供 IP 設計、驗證與整合能力。這是新型記憶體研發合作，尚未等同 HBM 產線建成。合作在日本 NEDO 補助的 Post-5G 基礎設施研發計畫下進行。官方公告著重工程支援與未來商業化意向，未披露交付規格和產線資本支出。ZAM 原型良率、傳輸頻寬、功耗測試、客戶樣品及商業量產日期尚未公布。</t>
           </r>
         </is>
       </c>
@@ -1034,17 +1034,128 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">對半導體製程電源、量測與測試設備供應商而言，值得追問的是桃園廠實際維持運轉的人力、受影響機台與在製品節點，以及台中協議是否涵蓋關鍵技術人員。現有資料不足以判定 DRAM、HBM 或封裝測試設備的拉貨與維護節奏會改變。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="194" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">追蹤：美光桃園 11 名工會幹部罷工，公布季度分潤及勞退調升
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">美光桃園工會 11 名幹部 10 月 22 日上午 9 時起展開 24 小時罷工，台中工會則已於前一天達成協議。美光同日公布季度分潤獎金採現金與股票各半，台灣員工勞退提撥率由 8% 提高至 10%，並增 3 天有薪假；實際產線損失仍未披露。桃園廠牽涉 DRAM 前段晶圓製造，台中廠有先進 DRAM、HBM 與封裝測試。工會幹部參與行動的實際規模，不能直接推算成整座晶圓廠停產時間。美光管理階層表示本次協議新增季度分潤，現金部分於每季財報後發放，股票獎勵一年後歸屬。公司亦公布輪班津貼和結構性調薪調整，桃園工會仍要求持續對話。未公布工廠產能利用率、實際出貨損失、桃園工會是否接受新方案及台中協議條款全文。地點：台灣桃園美光工廠外（實際工會行動地點，依中央社報導）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C22" s="6">
+        <v>46317</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">製程電源與記憶體測試供應商可核實罷工當日的輪班覆蓋、設備維護及在製品狀態，並留意薪酬協商對工廠排程是否有具體變動。現階段 11 名工會幹部的行動不足以估算設備需求或良率影響。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="214" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">馬來西亞 SkyeChip 與日本 SAIMEMORY 合作 ZAM 新型 AI 記憶體設計
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">日本 SAIMEMORY 與馬來西亞 SkyeChip 於 10 月 21 日宣布設計工程合作，由 SkyeChip 提供記憶體介面、矽晶片設計及客製化 IP，參與面向 AI 資料中心的 Z-Angle Memory（ZAM）開發。官方公告未提供原型測試結果、記憶體頻寬或量產時程。SAIMEMORY 為 SoftBank 旗下技術公司，ZAM 定位為高容量、高頻寬及降低功耗的記憶體架構；SkyeChip 提供 IP 設計、驗證與整合能力。這是新型記憶體研發合作，尚未等同 HBM 產線建成。合作在日本 NEDO 補助的 Post-5G 基礎設施研發計畫下進行。官方公告著重工程支援與未來商業化意向，未披露交付規格和產線資本支出。ZAM 原型良率、傳輸頻寬、功耗測試、客戶樣品及商業量產日期尚未公布。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C23" s="6">
+        <v>46316</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">記憶體電源、測試及高速介面供應商應查詢 ZAM 的實際電壓、頻寬、封裝介面與驗證方法。現階段缺少樣品量產、封裝基板及測試產能資訊。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="310" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
+    <row r="24" ht="214" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">追蹤：美光桃園工會 1,633 人反對方案，協商延期至 10 月 27 日
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">美光桃園工會 10 月 23 日公布會員投票，1,637 人參與、1,633 人反對公司 10 月 22 日公布的獎酬方案，工會稱反對人數約占全體會員七成。因颱風影響，原訂 10 月 23 日與美光的協商延至 10 月 27 日；沒有公告生產中斷或晶圓損失數字。桃園廠與 DRAM 前段晶圓製造相關，10 月 22 日由 11 名工會幹部進行的 24 小時罷工已於 23 日上午 9 時結束。此次新增資訊是會員投票與協商延期，而非再次發起罷工。美光此前公布季度分潤、輪班津貼和勞退提撥調整；工會認為方案未達其訴求。1,633 人占投票者約 99%，占全體工會會員近七成，兩個比例的分母不同。未取得可核對的工會完整會員名冊、雙方會議逐字稿或對產量、良率與交付的量化影響。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C24" s="6">
+        <v>46318</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">記憶體製程電源與封測設備服務業者可核對未來協商日期，以及實際機台維護人力是否受到影響。工會投票人數不能換算產能利用率或交期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="310" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1066,22 +1177,22 @@
           </r>
         </is>
       </c>
-      <c r="C22" s="6">
+      <c r="C25" s="6">
         <v>46314</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對資料中心電源轉換及量測業者而言，A201 的機櫃採購、液冷架構與通電驗收值得分開追問。集團利用率無法代替馬來西亞基地的負載測試，仍需確認實際上架、供電品質及客戶接受條件，不能據規劃容量推定設備需求已落實。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="242" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="26" ht="242" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1103,22 +1214,22 @@
           </r>
         </is>
       </c>
-      <c r="C23" s="6">
+      <c r="C26" s="6">
         <v>46314</v>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對機櫃電源、散熱控制與工廠量測供應商而言，三個廠區的產品分工及實際產線規格值得確認。公告還不足以判定新機櫃功率、設備驗收條件或需求時間，應將核准投資與已發包設備分開理解。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="210" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
+    <row r="27" ht="210" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1140,22 +1251,22 @@
           </r>
         </is>
       </c>
-      <c r="C24" s="6">
+      <c r="C27" s="6">
         <v>46314</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對資料中心電源轉換、配電量測及散熱控制業者而言，須先辨識意向容量對應的場址、業主與 GPU 營運分工。正式供電核定、機櫃規格及驗收時程均未公開，無法由 500MW 意向推定已成立的設備需求。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="226" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="28" ht="226" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1177,22 +1288,22 @@
           </r>
         </is>
       </c>
-      <c r="C25" s="6">
+      <c r="C28" s="6">
         <v>46316</v>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對資料中心電源、網路監控與測試設備供應商而言，應先確認合作是否延伸到海纜登陸站、備援供電、故障定位與維修協調，而不只政策對話。現階段沒有預算、採購與技術規格，不足以推論新增設備需求。</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="230" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
+    <row r="29" ht="230" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1214,22 +1325,96 @@
           </r>
         </is>
       </c>
-      <c r="C26" s="6">
+      <c r="C29" s="6">
         <v>46316</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">資料中心電源轉換、液冷 CDU、機櫃測試業者可核實箱體出廠的功能驗證範圍、現場變電與散熱介面，以及各 ODM 責任分工。最短部署時間仍是估計，尚無可比較的實際交付數據。</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="262" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="30" ht="198" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">神盾與法國 SiPearl 簽策略合作，推進 CPU Chiplet 平台
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">神盾集團 10 月 22 日在台灣舉辦的 2026 Tech Day 宣布與法國 SiPearl 簽署策略合作協議，涉及 CPU 技術、小晶片整合及高效能運算市場合作。旗下安國國際科技在 SiPearl 支援下開發 Mobius100 平台；雙方未披露產品出貨、資本支出或驗證日期。SiPearl 為無晶圓廠處理器設計商，合作與台灣晶片設計、先進封裝及高效能伺服器整機供應鏈有連結。簽訂策略協議不代表 CPU 已經完成設計驗證或客戶採購。中央社引述公司與經濟部說明，台法過去已有研發合作補助計畫，相關 2025 年投資數字僅為歷史背景，與新協議的投資金額不同。合作的核心授權條款、CPU 效能、製程節點、封裝方案、驗證進度及客戶名稱未公開。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C30" s="6">
+        <v>46317</v>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先進封裝電源與伺服器量測業者可確認 Mobius100 設計驗證、chiplet 介面及封裝測試需求，合作仍缺少產品技術規格與量產日期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="246" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">台灣公布 33 家新創赴新加坡 SWITCH 參展，聚焦半導體與機器人
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">國發會 10 月 23 日表示，10 月 27 日至 29 日將率領 33 家台灣新創赴新加坡 SWITCH 展會，參展規模為歷年最多，涵蓋半導體、機器人、AI 與永續能源。與投資機構和科技企業的對接為規劃活動，並未公布已成交投資或合作金額。新加坡 SWITCH 為跨境技術創新交流活動，台灣國家館由國發會聯合相關機關規劃，將安排國際創投、產業公司與研發合作交流。此項新公告涉及人才及科技投資生態系，尚無新增工廠產能。CNA 報導台灣館將安排台星新創論壇及 Taiwan Tech Connect 交流。SWITCH 官方網站確認活動 10 月 27 至 29 日在新加坡濱海灣金沙會議展覽中心舉行，場地包含 1 樓 A 至 C 展館及 3 樓宴會廳。尚未公布 33 家新創的最終投資、客戶簽約及技術驗證成果；上述為預定活動。地點：新加坡濱海灣金沙會議展覽中心，1 樓 A 至 C 展館及 3 樓宴會廳（預定展覽及會議場地）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C31" s="6">
+        <v>46318</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半導體量測與智慧工廠供應商可在活動後查閱具有實際技術驗證與供應鏈導入的合作公告。目前只有參展名額及規劃，無具體採購或合作成交量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="262" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1251,22 +1436,22 @@
           </r>
         </is>
       </c>
-      <c r="C27" s="6">
+      <c r="C32" s="6">
         <v>46311</v>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對電力轉換與量測控制供應商而言，相關客戶包括電池系統整合商與工商用戶，介面涉及 PCS、EMS 及現場驗收。值得核對額定功率、通訊規格與認證要求；306kWh 與 100 MWh 分別是規格及目標，不能據以推算已下單的轉換器數量。</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="178" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
+    <row r="33" ht="178" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1288,22 +1473,22 @@
           </r>
         </is>
       </c>
-      <c r="C28" s="6">
+      <c r="C33" s="6">
         <v>46313</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對工業電源與量測控制設備業者而言，相關節點包括安裝後電氣測試、控制系統驗證與併網驗收。值得確認的是驗收依據及付款機制如何適用於設備供應與分包；目前缺少原始契約與最終清償安排，不能由安裝數推定回款。</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="262" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="34" ht="262" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1325,22 +1510,22 @@
           </r>
         </is>
       </c>
-      <c r="C29" s="6">
+      <c r="C34" s="6">
         <v>46315</v>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">精密電源、量測及控制設備供應商會先確認投資案中有哪些涉及晶圓製造、封裝或工廠自動化，以及進度是否進入正式採購。官方公告尚未將 6,660 億元逐案分配，也未提供驗收時程，無法作為訂單預測。</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="294" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+    <row r="35" ht="294" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1362,22 +1547,22 @@
           </r>
         </is>
       </c>
-      <c r="C30" s="6">
+      <c r="C35" s="6">
         <v>46315</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對電源轉換、量測與自動化設備業者而言，鹿特丹港試用後取得訂單的資訊比單純展出更接近商業驗證，但仍應區分 2027 年規劃導入與當前實際部署。產發署尚未披露契約金額、設備數量或採購流程。</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="210" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="36" ht="210" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1399,22 +1584,22 @@
           </r>
         </is>
       </c>
-      <c r="C31" s="6">
+      <c r="C36" s="6">
         <v>46315</v>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">工業控制與量測設備商可從監測精度、警報誤報率、設備連線方式與既有廠務系統相容性查核示範範圍。官方尚未公布裝機量與同口徑改善數據，難以評估跨工廠複製程度。</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="210" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
+    <row r="37" ht="210" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1436,22 +1621,22 @@
           </r>
         </is>
       </c>
-      <c r="C32" s="6">
+      <c r="C37" s="6">
         <v>46315</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對半導體製程設備與精密電源供應商而言，後續應核對哪些新廠的鋼構、廠務與機台進場屬同一關鍵路徑，以及現場承攬商的復工條件。未公布停工天數與設備搬入節點前，不能判定裝機、驗收或服務時程已改變。</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="242" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="38" ht="242" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1473,22 +1658,22 @@
           </r>
         </is>
       </c>
-      <c r="C33" s="6">
+      <c r="C38" s="6">
         <v>46316</v>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對精密製造設備、量測與控制方案供應商而言，可追蹤補助是否涵蓋設備資料介接、預測維護、製程控制與報價自動化，以及半導體案例的實際部署規模。計畫金額屬政策承諾，未公布受惠企業與採購清單，現階段不足以判定硬體需求。</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="178" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
+    <row r="39" ht="178" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1510,22 +1695,22 @@
           </r>
         </is>
       </c>
-      <c r="C34" s="6">
+      <c r="C39" s="6">
         <v>46317</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對半導體設備電源、驅動器與精密控制業者，需確認是否涉及磁性材料變更、效率與可靠度測試及機台重新認證。原廠未證實導入，缺乏替換量及設備驗證時程。</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="194" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="40" ht="194" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1547,12 +1732,86 @@
           </r>
         </is>
       </c>
-      <c r="C35" s="6">
+      <c r="C40" s="6">
         <v>46317</v>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">對半導體設備服務、製程量測與自動化廠商可核對人才培訓課程涵蓋的設備操作技能與具體職務分布。核准名額、累計完訓及最終就業人數採不同口徑，還不足以推估廠商招募情況。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="194" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">漢翔台中廠啟用 9MW／54MWh 工業微電網，最高備援 6 小時
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">漢翔航空工業 10 月 22 日在台中水湳廠啟用 9MW／54MWh 微電網，整合電池儲能、能源管理、控制和電力保護。公司稱可提供全廠最高 6 小時供電備援，依既有電價條件估計年能源成本可降低近 40%；節費比例仍為評估數。此表後儲能系統可透過離峰充電、尖峰放電管理工廠需量，亦可與風力、太陽光電及備援機組連結。案例涉及工廠配電、電源控制、電池管理和資料中心類型負載的供電需求。公司宣稱具備孤島運轉及多層電氣安全保護功能，台電夏季尖離峰電價差每度 9.29 元被用於節費試算。2025 年先前 2MW／2.7MWh 示範案為背景，與本次啟用的 9MW／54MWh 案不同。未公布完整年度節費實績、設備供應商合約金額、系統效率和各負載的備援測試分布。地點：台灣台中市水湳廠區（已啟用工業電力島案場）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C41" s="6">
+        <v>46317</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工業電源與儲能供應商可檢視島狀運轉轉換時間、負載耐受與實際尖離峰用電；節費 40% 的公司估算仍須長期運轉驗證。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="178" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="13"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF14322B"/>
+            </rPr>
+            <t xml:space="preserve">國際貿易署更新高科技貨品實體名單：新增 343 個、移除 90 個
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="PingFang TC"/>
+              <color rgb="FF3B4A44"/>
+            </rPr>
+            <t xml:space="preserve">經濟部國際貿易署 10 月 22 日公告，戰略性高科技貨品出口實體管理名單新增 343 個實體、移除 90 個，依貿易法第 13 條辦理。向名單上受管制對象出口相關貨品須事先取得戰略性高科技貨品輸出許可，海關會執行相關查核。涉及軍商兩用貨品及技術的管理範圍，可涵蓋特定半導體設備、電子、材料加工、電腦和感測器，但是否需要許可，仍取決於貨品分類、交易對象及最終用途。官方指出目前逾 11,660 個實體與個人列入管理名單，10 月 22 日新增分布於伊朗、俄羅斯、墨西哥、阿聯、土耳其及中國等地；更新名單已公開。官方新聞稿未逐一列出各台灣企業是否有受影響交易，也未提供依產業分類的輸出貨值變化。</t>
+          </r>
+        </is>
+      </c>
+      <c r="C42" s="6">
+        <v>46317</v>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">設備與測試供應商可核對零件分類、最終用途及官方名單更新與既有出口許可條件是否涉及同一交易；本文無法從實體數量推估出口金額變化。</t>
         </is>
       </c>
     </row>
